--- a/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
+++ b/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wanho\Documents\kate_gait_subjective\gaitanalysersubjective\app\jsonfiles\excel\stance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEEAF6A0-098A-4110-BC9E-64C3F4725A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B534366C-8CDF-4CC0-B45E-1BD148F61E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="treatments" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="258">
   <si>
     <t>label</t>
   </si>
@@ -459,9 +459,6 @@
     <t>possible_impairments</t>
   </si>
   <si>
-    <t>[18,20]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Decreased strength in ankle dorsiflexors (concentric) </t>
   </si>
   <si>
@@ -490,9 +487,6 @@
   </si>
   <si>
     <t>Hip abduction strengthening in gravity eliminated position; consider using tactile cues for movement targets to provide augmented feedback for successful repetition.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical stimulation to increase strength of hip adductors  +/- mental practice </t>
   </si>
   <si>
     <t>Hip adduction strengthening in gravity eliminated position; consider using tactile cues for movement targets to provide augmented feedback for successful repetition.</t>
@@ -608,16 +602,7 @@
     <t>[2,3,4,5,23]</t>
   </si>
   <si>
-    <t>[4,6,8,14,16,23]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Plantarflexor power training using trampoline, or jumping device </t>
-  </si>
-  <si>
-    <t>Treatments to target eccentric control of hip flexors</t>
-  </si>
-  <si>
-    <t>Treatments to target eccentric control of knee flexors</t>
   </si>
   <si>
     <t xml:space="preserve">Decreased strength hip adductors (early to mid stance) </t>
@@ -729,9 +714,6 @@
     <t>[14,13,16,18,19,59]</t>
   </si>
   <si>
-    <t>[12,21,26]</t>
-  </si>
-  <si>
     <t>Decreased strength of knee flexors prior to and immediately after heelstrike (concentric, eccentric)</t>
   </si>
   <si>
@@ -744,22 +726,13 @@
     <t>[6,14,15]</t>
   </si>
   <si>
-    <t>[51]</t>
-  </si>
-  <si>
     <t>Hip flexion strengthening in sitting or lying with a focus on the eccentric phase</t>
   </si>
   <si>
-    <t>[23]</t>
-  </si>
-  <si>
     <t>[33,64]</t>
   </si>
   <si>
     <t>[5,6,14,16,17,18,19,23]</t>
-  </si>
-  <si>
-    <t>[29,20,24,14,16]</t>
   </si>
   <si>
     <t>[65,66]</t>
@@ -994,12 +967,6 @@
     <t>COORDINATION: Inability to coordinate leg extension with controlled weight shift onto stance leg</t>
   </si>
   <si>
-    <t>STRENGTH: Decreased strength hip abductors (eccentric, concentric)</t>
-  </si>
-  <si>
-    <t>STRENGTH: Decreased strength of knee flexors prior to and immediately after heelstrike (concentric, eccentric)</t>
-  </si>
-  <si>
     <t xml:space="preserve">STRENGTH: Decreased strength hip adductors (early to mid stance) </t>
   </si>
   <si>
@@ -1285,9 +1252,6 @@
     </r>
   </si>
   <si>
-    <t>Electrical stimulation to increase strength of hip extension - DELETE AS NON PRACTICAL</t>
-  </si>
-  <si>
     <t>If severe contracture: consider serial casting.</t>
   </si>
   <si>
@@ -1300,12 +1264,6 @@
     <t>["ankle_dorsiflexion", "ankle_plantarflexion","knee_flexion"]</t>
   </si>
   <si>
-    <t>["knee_extension","knee_flexion"]</t>
-  </si>
-  <si>
-    <t>["concentric_str","eccentric_str"]</t>
-  </si>
-  <si>
     <t>hip_adduction</t>
   </si>
   <si>
@@ -1316,13 +1274,61 @@
   </si>
   <si>
     <t>image</t>
+  </si>
+  <si>
+    <t>STRENGTH: Decreased strength hip abductors (concentric)</t>
+  </si>
+  <si>
+    <t>STRENGTH: Decreased strength hip abductors (eccentric)</t>
+  </si>
+  <si>
+    <t>STRENGTH: Decreased strength of knee flexors  (eccentric)</t>
+  </si>
+  <si>
+    <t>[12,11,21,26]</t>
+  </si>
+  <si>
+    <t>[18,20,29,24,14,16]</t>
+  </si>
+  <si>
+    <t>[18,20,29]</t>
+  </si>
+  <si>
+    <t>[4,6,8,9,14,16,23]</t>
+  </si>
+  <si>
+    <t>["ankle_plantarflexion","knee_flexion"]</t>
+  </si>
+  <si>
+    <t>["ankle_dorsiflexion","knee_flexion"]</t>
+  </si>
+  <si>
+    <t>["https://app.magicapp.org/#/guideline/Kj2R8j/section/LrwOWn"]</t>
+  </si>
+  <si>
+    <t>["https://app.magicapp.org/#/guideline/Kj2R8j/section/Eglqdj"]</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>Hip extensors strengthening against gravity with therabands, apply principles of progressive resistance training</t>
+  </si>
+  <si>
+    <t>Hip extensors strengthening in gravity elimminated positions.</t>
+  </si>
+  <si>
+    <t>[5167,68]</t>
+  </si>
+  <si>
+    <t>["knee_flexion","knee_extension"]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1352,14 +1358,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FF92D050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1397,7 +1395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1406,8 +1404,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1821,7 +1817,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1830,7 +1826,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1854,10 +1850,10 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="J1" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1">
@@ -1885,6 +1881,9 @@
       <c r="H2" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I2" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="J2" s="2" t="str">
         <f>CONCATENATE("walking","_","Tx",A2)</f>
         <v>walking_Tx2</v>
@@ -1915,8 +1914,11 @@
       <c r="H3" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I3" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J3" s="2" t="str">
-        <f t="shared" ref="J3:J64" si="0">CONCATENATE("walking","_","Tx",A3)</f>
+        <f t="shared" ref="J3:J60" si="0">CONCATENATE("walking","_","Tx",A3)</f>
         <v>walking_Tx3</v>
       </c>
     </row>
@@ -1945,6 +1947,9 @@
       <c r="H4" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I4" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J4" s="2" t="str">
         <f>CONCATENATE("walking","_","Tx",A4)</f>
         <v>walking_Tx4</v>
@@ -1975,6 +1980,9 @@
       <c r="H5" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I5" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx5</v>
@@ -1985,7 +1993,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -2004,6 +2012,9 @@
       </c>
       <c r="H6" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2015,7 +2026,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2">
         <v>3</v>
@@ -2034,6 +2045,9 @@
       </c>
       <c r="H7" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2044,7 +2058,7 @@
       <c r="A8" s="2">
         <v>8</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>80</v>
       </c>
       <c r="C8" s="2">
@@ -2064,6 +2078,9 @@
       </c>
       <c r="H8" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="J8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2095,6 +2112,9 @@
       <c r="H9" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I9" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx9</v>
@@ -2125,6 +2145,9 @@
       <c r="H10" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I10" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx10</v>
@@ -2155,6 +2178,9 @@
       <c r="H11" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I11" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J11" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx11</v>
@@ -2185,6 +2211,9 @@
       <c r="H12" t="b">
         <v>0</v>
       </c>
+      <c r="I12" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="J12" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx12</v>
@@ -2195,7 +2224,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -2214,6 +2243,9 @@
       </c>
       <c r="H13" t="b">
         <v>0</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="0"/>
@@ -2225,7 +2257,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2">
         <v>3</v>
@@ -2244,6 +2276,9 @@
       </c>
       <c r="H14" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="J14" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2255,7 +2290,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C15" s="2">
         <v>3</v>
@@ -2274,6 +2309,9 @@
       </c>
       <c r="H15" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="J15" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2285,7 +2323,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
@@ -2304,6 +2342,9 @@
       </c>
       <c r="H16" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="J16" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2335,6 +2376,9 @@
       <c r="H17" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I17" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J17" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx17</v>
@@ -2365,6 +2409,9 @@
       <c r="H18" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I18" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J18" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx18</v>
@@ -2375,7 +2422,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
@@ -2394,6 +2441,9 @@
       </c>
       <c r="H19" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="J19" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2405,7 +2455,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
@@ -2424,6 +2474,9 @@
       </c>
       <c r="H20" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="J20" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2455,6 +2508,9 @@
       <c r="H21" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I21" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J21" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx21</v>
@@ -2465,7 +2521,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -2484,6 +2540,9 @@
       </c>
       <c r="H22" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="J22" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2515,6 +2574,9 @@
       <c r="H23" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I23" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J23" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx23</v>
@@ -2525,7 +2587,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
@@ -2544,6 +2606,9 @@
       </c>
       <c r="H24" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="J24" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2575,6 +2640,9 @@
       <c r="H25" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I25" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J25" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx25</v>
@@ -2585,7 +2653,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
@@ -2604,6 +2672,9 @@
       </c>
       <c r="H26" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="J26" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2615,7 +2686,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C27" s="2">
         <v>2</v>
@@ -2634,6 +2705,9 @@
       </c>
       <c r="H27" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="J27" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2665,6 +2739,9 @@
       <c r="H28" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I28" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J28" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx28</v>
@@ -2695,6 +2772,9 @@
       <c r="H29" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I29" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J29" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx29</v>
@@ -2725,6 +2805,9 @@
       <c r="H30" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I30" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J30" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx30</v>
@@ -2755,6 +2838,9 @@
       <c r="H31" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I31" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J31" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx31</v>
@@ -2785,6 +2871,9 @@
       <c r="H32" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I32" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="J32" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx32</v>
@@ -2795,7 +2884,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -2814,6 +2903,9 @@
       </c>
       <c r="H33" t="b">
         <v>1</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="J33" t="str">
         <f t="shared" si="0"/>
@@ -2825,7 +2917,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2844,6 +2936,9 @@
       </c>
       <c r="H34" t="b">
         <v>0</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J34" t="str">
         <f t="shared" si="0"/>
@@ -2855,7 +2950,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -2874,6 +2969,9 @@
       </c>
       <c r="H35" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J35" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2885,7 +2983,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -2904,6 +3002,9 @@
       </c>
       <c r="H36" t="b">
         <v>0</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J36" t="str">
         <f t="shared" si="0"/>
@@ -2935,6 +3036,9 @@
       <c r="H37" t="b">
         <v>0</v>
       </c>
+      <c r="I37" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="J37" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx37</v>
@@ -2945,7 +3049,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2964,6 +3068,9 @@
       </c>
       <c r="H38" t="b">
         <v>1</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="J38" t="str">
         <f t="shared" si="0"/>
@@ -2975,7 +3082,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2994,6 +3101,9 @@
       </c>
       <c r="H39" t="b">
         <v>0</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J39" t="str">
         <f t="shared" si="0"/>
@@ -3025,6 +3135,9 @@
       <c r="H40" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I40" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="J40" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx40</v>
@@ -3055,6 +3168,9 @@
       <c r="H41" t="b">
         <v>1</v>
       </c>
+      <c r="I41" s="2" t="s">
+        <v>253</v>
+      </c>
       <c r="J41" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx41</v>
@@ -3085,6 +3201,9 @@
       <c r="H42" t="b">
         <v>0</v>
       </c>
+      <c r="I42" s="2" t="s">
+        <v>253</v>
+      </c>
       <c r="J42" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx42</v>
@@ -3095,7 +3214,7 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -3114,6 +3233,9 @@
       </c>
       <c r="H43" t="b">
         <v>0</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J43" t="str">
         <f t="shared" si="0"/>
@@ -3125,7 +3247,7 @@
         <v>45</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -3144,6 +3266,9 @@
       </c>
       <c r="H44" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J44" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3155,7 +3280,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3174,6 +3299,9 @@
       </c>
       <c r="H45" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J45" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3185,7 +3313,7 @@
         <v>47</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3204,6 +3332,9 @@
       </c>
       <c r="H46" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J46" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3215,7 +3346,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C47" s="2">
         <v>2</v>
@@ -3234,6 +3365,9 @@
       </c>
       <c r="H47" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J47" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3245,7 +3379,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -3264,174 +3398,192 @@
       </c>
       <c r="H48" t="b">
         <v>0</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J48" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx49</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
-      <c r="A49">
-        <v>50</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-      <c r="E49" t="b">
-        <v>0</v>
-      </c>
-      <c r="F49" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" t="b">
-        <v>0</v>
-      </c>
-      <c r="J49" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx50</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" s="2" customFormat="1">
-      <c r="A50" s="2">
+    <row r="49" spans="1:10" s="2" customFormat="1">
+      <c r="A49" s="2">
         <v>51</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C50" s="2">
-        <v>1</v>
-      </c>
-      <c r="D50" s="2">
+      <c r="B49" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2">
         <v>2</v>
       </c>
-      <c r="E50" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" s="2" t="str">
+      <c r="E49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J49" s="2" t="str">
         <f t="shared" si="0"/>
         <v>walking_Tx51</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
-      <c r="A51">
-        <v>53</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-      <c r="E51" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" t="b">
-        <v>0</v>
-      </c>
-      <c r="H51" t="b">
-        <v>0</v>
-      </c>
-      <c r="J51" t="str">
+    <row r="50" spans="1:10">
+      <c r="A50">
+        <v>56</v>
+      </c>
+      <c r="B50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J50" t="str">
         <f t="shared" si="0"/>
-        <v>walking_Tx53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52">
-        <v>54</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-      <c r="E52" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" t="b">
-        <v>0</v>
-      </c>
-      <c r="H52" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" t="str">
+        <v>walking_Tx56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" s="2" customFormat="1">
+      <c r="A51" s="2">
+        <v>57</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="2">
+        <v>2</v>
+      </c>
+      <c r="D51" s="2">
+        <v>1</v>
+      </c>
+      <c r="E51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J51" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>walking_Tx54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53">
-        <v>55</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" t="b">
-        <v>0</v>
-      </c>
-      <c r="H53" t="b">
-        <v>0</v>
-      </c>
-      <c r="J53" t="str">
+        <v>walking_Tx57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" s="2" customFormat="1">
+      <c r="A52" s="2">
+        <v>58</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" s="2">
+        <v>2</v>
+      </c>
+      <c r="D52" s="2">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J52" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>walking_Tx55</v>
+        <v>walking_Tx58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" s="2" customFormat="1">
+      <c r="A53" s="2">
+        <v>59</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="2">
+        <v>3</v>
+      </c>
+      <c r="D53" s="2">
+        <v>1</v>
+      </c>
+      <c r="E53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J53" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx59</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54">
-        <v>56</v>
-      </c>
-      <c r="B54" t="s">
-        <v>112</v>
+        <v>60</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -3444,21 +3596,24 @@
       </c>
       <c r="H54" t="b">
         <v>0</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="J54" t="str">
         <f t="shared" si="0"/>
-        <v>walking_Tx56</v>
+        <v>walking_Tx60</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="2" customFormat="1">
       <c r="A55" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C55" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" s="2">
         <v>1</v>
@@ -3474,18 +3629,21 @@
       </c>
       <c r="H55" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="J55" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>walking_Tx57</v>
+        <v>walking_Tx61</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="2" customFormat="1">
       <c r="A56" s="2">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="C56" s="2">
         <v>2</v>
@@ -3505,53 +3663,59 @@
       <c r="H56" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I56" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="J56" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>walking_Tx58</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" s="2" customFormat="1">
-      <c r="A57" s="2">
-        <v>59</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C57" s="2">
+        <v>walking_Tx62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57">
+        <v>63</v>
+      </c>
+      <c r="B57" t="s">
+        <v>175</v>
+      </c>
+      <c r="C57">
         <v>3</v>
       </c>
-      <c r="D57" s="2">
-        <v>1</v>
-      </c>
-      <c r="E57" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J57" s="2" t="str">
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J57" t="str">
         <f t="shared" si="0"/>
-        <v>walking_Tx59</v>
+        <v>walking_Tx63</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58">
-        <v>60</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>246</v>
+        <v>64</v>
+      </c>
+      <c r="B58" t="s">
+        <v>235</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -3564,48 +3728,54 @@
       </c>
       <c r="H58" t="b">
         <v>0</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="J58" t="str">
         <f t="shared" si="0"/>
-        <v>walking_Tx60</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" s="2" customFormat="1">
-      <c r="A59" s="2">
-        <v>61</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C59" s="2">
-        <v>3</v>
-      </c>
-      <c r="D59" s="2">
-        <v>1</v>
-      </c>
-      <c r="E59" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F59" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" s="2" t="str">
+        <v>walking_Tx64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59">
+        <v>65</v>
+      </c>
+      <c r="B59" t="s">
+        <v>110</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59" t="b">
+        <v>0</v>
+      </c>
+      <c r="F59" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J59" t="str">
         <f t="shared" si="0"/>
-        <v>walking_Tx61</v>
+        <v>walking_Tx65</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="2" customFormat="1">
       <c r="A60" s="2">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C60" s="2">
         <v>2</v>
@@ -3625,20 +3795,23 @@
       <c r="H60" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="I60" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="J60" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>walking_Tx62</v>
+        <v>walking_Tx66</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>182</v>
+        <v>254</v>
       </c>
       <c r="C61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3655,20 +3828,23 @@
       <c r="H61" t="b">
         <v>0</v>
       </c>
+      <c r="I61" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="J61" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx63</v>
+        <f t="shared" ref="J61" si="1">CONCATENATE("walking","_","Tx",A61)</f>
+        <v>walking_Tx67</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3685,69 +3861,12 @@
       <c r="H62" t="b">
         <v>0</v>
       </c>
+      <c r="I62" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="J62" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx64</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63">
-        <v>65</v>
-      </c>
-      <c r="B63" t="s">
-        <v>112</v>
-      </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" t="b">
-        <v>1</v>
-      </c>
-      <c r="G63" t="b">
-        <v>0</v>
-      </c>
-      <c r="H63" t="b">
-        <v>0</v>
-      </c>
-      <c r="J63" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx65</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" s="2" customFormat="1">
-      <c r="A64" s="2">
-        <v>66</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C64" s="2">
-        <v>2</v>
-      </c>
-      <c r="D64" s="2">
-        <v>1</v>
-      </c>
-      <c r="E64" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F64" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H64" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J64" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx66</v>
+        <f t="shared" ref="J62" si="2">CONCATENATE("walking","_","Tx",A62)</f>
+        <v>walking_Tx68</v>
       </c>
     </row>
   </sheetData>
@@ -3769,7 +3888,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -3786,40 +3905,40 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3830,51 +3949,51 @@
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>188</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>186</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -3885,7 +4004,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:IA29"/>
+  <dimension ref="A1:IA30"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.6"/>
   <cols>
     <col min="2" max="2" width="60.8984375" customWidth="1"/>
@@ -3896,7 +4015,7 @@
   <sheetData>
     <row r="1" spans="1:235">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B1" t="s">
         <v>7</v>
@@ -3919,13 +4038,13 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -4168,16 +4287,16 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>250</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
@@ -4417,16 +4536,16 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E4" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -4666,10 +4785,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -4915,16 +5034,16 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
         <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>249</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
@@ -5164,13 +5283,13 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -5413,16 +5532,16 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E8" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
@@ -5662,16 +5781,16 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D9" t="s">
         <v>62</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>249</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
@@ -5911,10 +6030,10 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C10" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D10" t="s">
         <v>64</v>
@@ -6160,10 +6279,10 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
         <v>65</v>
@@ -6409,13 +6528,13 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
@@ -6658,10 +6777,10 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
         <v>61</v>
@@ -6907,10 +7026,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
         <v>67</v>
@@ -7156,13 +7275,13 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C15" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -7405,10 +7524,10 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C16" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="D16" t="s">
         <v>69</v>
@@ -7654,10 +7773,10 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
         <v>70</v>
@@ -7903,13 +8022,13 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C18" t="s">
-        <v>183</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E18" t="s">
         <v>22</v>
@@ -8152,10 +8271,10 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="C19" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D19" t="s">
         <v>61</v>
@@ -8401,10 +8520,10 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
         <v>72</v>
@@ -8413,7 +8532,7 @@
         <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>251</v>
+        <v>13</v>
       </c>
       <c r="G20"/>
       <c r="H20"/>
@@ -8650,19 +8769,19 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="E21" t="s">
         <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>251</v>
+        <v>13</v>
       </c>
       <c r="G21"/>
       <c r="H21"/>
@@ -8899,10 +9018,10 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
         <v>75</v>
@@ -9148,10 +9267,10 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C23" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D23" t="s">
         <v>75</v>
@@ -9168,19 +9287,19 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="C24" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D24" t="s">
         <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:235">
@@ -9188,10 +9307,10 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C25" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D25" t="s">
         <v>75</v>
@@ -9208,10 +9327,10 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
         <v>75</v>
@@ -9228,10 +9347,10 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
         <v>75</v>
@@ -9248,10 +9367,10 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
         <v>75</v>
@@ -9268,25 +9387,262 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
-      </c>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:235" s="2" customFormat="1">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30"/>
+      <c r="S30"/>
+      <c r="T30"/>
+      <c r="U30"/>
+      <c r="V30"/>
+      <c r="W30"/>
+      <c r="X30"/>
+      <c r="Y30"/>
+      <c r="Z30"/>
+      <c r="AA30"/>
+      <c r="AB30"/>
+      <c r="AC30"/>
+      <c r="AD30"/>
+      <c r="AE30"/>
+      <c r="AF30"/>
+      <c r="AG30"/>
+      <c r="AH30"/>
+      <c r="AI30"/>
+      <c r="AJ30"/>
+      <c r="AK30"/>
+      <c r="AL30"/>
+      <c r="AM30"/>
+      <c r="AN30"/>
+      <c r="AO30"/>
+      <c r="AP30"/>
+      <c r="AQ30"/>
+      <c r="AR30"/>
+      <c r="AS30"/>
+      <c r="AT30"/>
+      <c r="AU30"/>
+      <c r="AV30"/>
+      <c r="AW30"/>
+      <c r="AX30"/>
+      <c r="AY30"/>
+      <c r="AZ30"/>
+      <c r="BA30"/>
+      <c r="BB30"/>
+      <c r="BC30"/>
+      <c r="BD30"/>
+      <c r="BE30"/>
+      <c r="BF30"/>
+      <c r="BG30"/>
+      <c r="BH30"/>
+      <c r="BI30"/>
+      <c r="BJ30"/>
+      <c r="BK30"/>
+      <c r="BL30"/>
+      <c r="BM30"/>
+      <c r="BN30"/>
+      <c r="BO30"/>
+      <c r="BP30"/>
+      <c r="BQ30"/>
+      <c r="BR30"/>
+      <c r="BS30"/>
+      <c r="BT30"/>
+      <c r="BU30"/>
+      <c r="BV30"/>
+      <c r="BW30"/>
+      <c r="BX30"/>
+      <c r="BY30"/>
+      <c r="BZ30"/>
+      <c r="CA30"/>
+      <c r="CB30"/>
+      <c r="CC30"/>
+      <c r="CD30"/>
+      <c r="CE30"/>
+      <c r="CF30"/>
+      <c r="CG30"/>
+      <c r="CH30"/>
+      <c r="CI30"/>
+      <c r="CJ30"/>
+      <c r="CK30"/>
+      <c r="CL30"/>
+      <c r="CM30"/>
+      <c r="CN30"/>
+      <c r="CO30"/>
+      <c r="CP30"/>
+      <c r="CQ30"/>
+      <c r="CR30"/>
+      <c r="CS30"/>
+      <c r="CT30"/>
+      <c r="CU30"/>
+      <c r="CV30"/>
+      <c r="CW30"/>
+      <c r="CX30"/>
+      <c r="CY30"/>
+      <c r="CZ30"/>
+      <c r="DA30"/>
+      <c r="DB30"/>
+      <c r="DC30"/>
+      <c r="DD30"/>
+      <c r="DE30"/>
+      <c r="DF30"/>
+      <c r="DG30"/>
+      <c r="DH30"/>
+      <c r="DI30"/>
+      <c r="DJ30"/>
+      <c r="DK30"/>
+      <c r="DL30"/>
+      <c r="DM30"/>
+      <c r="DN30"/>
+      <c r="DO30"/>
+      <c r="DP30"/>
+      <c r="DQ30"/>
+      <c r="DR30"/>
+      <c r="DS30"/>
+      <c r="DT30"/>
+      <c r="DU30"/>
+      <c r="DV30"/>
+      <c r="DW30"/>
+      <c r="DX30"/>
+      <c r="DY30"/>
+      <c r="DZ30"/>
+      <c r="EA30"/>
+      <c r="EB30"/>
+      <c r="EC30"/>
+      <c r="ED30"/>
+      <c r="EE30"/>
+      <c r="EF30"/>
+      <c r="EG30"/>
+      <c r="EH30"/>
+      <c r="EI30"/>
+      <c r="EJ30"/>
+      <c r="EK30"/>
+      <c r="EL30"/>
+      <c r="EM30"/>
+      <c r="EN30"/>
+      <c r="EO30"/>
+      <c r="EP30"/>
+      <c r="EQ30"/>
+      <c r="ER30"/>
+      <c r="ES30"/>
+      <c r="ET30"/>
+      <c r="EU30"/>
+      <c r="EV30"/>
+      <c r="EW30"/>
+      <c r="EX30"/>
+      <c r="EY30"/>
+      <c r="EZ30"/>
+      <c r="FA30"/>
+      <c r="FB30"/>
+      <c r="FC30"/>
+      <c r="FD30"/>
+      <c r="FE30"/>
+      <c r="FF30"/>
+      <c r="FG30"/>
+      <c r="FH30"/>
+      <c r="FI30"/>
+      <c r="FJ30"/>
+      <c r="FK30"/>
+      <c r="FL30"/>
+      <c r="FM30"/>
+      <c r="FN30"/>
+      <c r="FO30"/>
+      <c r="FP30"/>
+      <c r="FQ30"/>
+      <c r="FR30"/>
+      <c r="FS30"/>
+      <c r="FT30"/>
+      <c r="FU30"/>
+      <c r="FV30"/>
+      <c r="FW30"/>
+      <c r="FX30"/>
+      <c r="FY30"/>
+      <c r="FZ30"/>
+      <c r="GA30"/>
+      <c r="GB30"/>
+      <c r="GC30"/>
+      <c r="GD30"/>
+      <c r="GE30"/>
+      <c r="GF30"/>
+      <c r="GG30"/>
+      <c r="GH30"/>
+      <c r="GI30"/>
+      <c r="GJ30"/>
+      <c r="GK30"/>
+      <c r="GL30"/>
+      <c r="GM30"/>
+      <c r="GN30"/>
+      <c r="GO30"/>
+      <c r="GP30"/>
+      <c r="GQ30"/>
+      <c r="GR30"/>
+      <c r="GS30"/>
+      <c r="GT30"/>
+      <c r="GU30"/>
+      <c r="GV30"/>
+      <c r="GW30"/>
+      <c r="GX30"/>
+      <c r="GY30"/>
+      <c r="GZ30"/>
+      <c r="HA30"/>
+      <c r="HB30"/>
+      <c r="HC30"/>
+      <c r="HD30"/>
+      <c r="HE30"/>
+      <c r="HF30"/>
+      <c r="HG30"/>
+      <c r="HH30"/>
+      <c r="HI30"/>
+      <c r="HJ30"/>
+      <c r="HK30"/>
+      <c r="HL30"/>
+      <c r="HM30"/>
+      <c r="HN30"/>
+      <c r="HO30"/>
+      <c r="HP30"/>
+      <c r="HQ30"/>
+      <c r="HR30"/>
+      <c r="HS30"/>
+      <c r="HT30"/>
+      <c r="HU30"/>
+      <c r="HV30"/>
+      <c r="HW30"/>
+      <c r="HX30"/>
+      <c r="HY30"/>
+      <c r="HZ30"/>
+      <c r="IA30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="B1 D1 F1 F4 E5:F5 E6 E7:F7 F8 E9 E10:F10 E11:F11 E12:F12 E13:F13 E14:F14 E15:F15 E16:F16 E17 E18:F18 E19:F19 E20 F3" numberStoredAsText="1"/>
+    <ignoredError sqref="B1 D1 F1 F4 E5:F5 E7:F7 F8 E10:F10 E11:F11 E12:F12 E13:F13 F14 E15:F15 E16 E17 E18:F18 E19:F19 E20 F3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9309,46 +9665,46 @@
     </row>
     <row r="2" spans="1:4" ht="78">
       <c r="A2" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="156">
       <c r="B3" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="31.2">
       <c r="B4" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="187.2">
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -9356,10 +9712,10 @@
     </row>
     <row r="6" spans="1:4" ht="62.4">
       <c r="B6" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
         <v>75</v>
@@ -9367,24 +9723,24 @@
     </row>
     <row r="7" spans="1:4" ht="46.8">
       <c r="A7" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="187.2">
       <c r="B8" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D8" t="s">
         <v>61</v>
@@ -9395,7 +9751,7 @@
         <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D9" t="s">
         <v>62</v>
@@ -9406,10 +9762,10 @@
         <v>49</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="187.2">
@@ -9417,7 +9773,7 @@
         <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
         <v>67</v>
@@ -9425,10 +9781,10 @@
     </row>
     <row r="12" spans="1:4" ht="156">
       <c r="B12" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D12" t="s">
         <v>75</v>
@@ -9436,16 +9792,16 @@
     </row>
     <row r="13" spans="1:4" ht="46.8">
       <c r="A13" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="374.4">
@@ -9453,7 +9809,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D14" t="s">
         <v>62</v>
@@ -9464,7 +9820,7 @@
         <v>52</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D15" t="s">
         <v>64</v>
@@ -9472,13 +9828,13 @@
     </row>
     <row r="16" spans="1:4" ht="156">
       <c r="A16" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D16" t="s">
         <v>66</v>
@@ -9486,10 +9842,10 @@
     </row>
     <row r="17" spans="1:4" ht="109.2">
       <c r="B17" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s">
         <v>73</v>
@@ -9497,10 +9853,10 @@
     </row>
     <row r="18" spans="1:4" ht="156">
       <c r="B18" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D18" t="s">
         <v>75</v>
@@ -9508,13 +9864,13 @@
     </row>
     <row r="19" spans="1:4" ht="234">
       <c r="A19" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D19" t="s">
         <v>62</v>
@@ -9525,7 +9881,7 @@
         <v>54</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
         <v>67</v>
@@ -9536,7 +9892,7 @@
         <v>55</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D21" t="s">
         <v>68</v>
@@ -9544,13 +9900,13 @@
     </row>
     <row r="22" spans="1:4" ht="187.2">
       <c r="A22" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D22" t="s">
         <v>61</v>
@@ -9561,7 +9917,7 @@
         <v>48</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D23" t="s">
         <v>62</v>
@@ -9572,7 +9928,7 @@
         <v>54</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D24" t="s">
         <v>67</v>
@@ -9583,7 +9939,7 @@
         <v>56</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
         <v>69</v>
@@ -9594,7 +9950,7 @@
         <v>57</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D26" t="s">
         <v>70</v>
@@ -9616,7 +9972,7 @@
         <v>60</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D28" t="s">
         <v>61</v>
@@ -9624,10 +9980,10 @@
     </row>
     <row r="29" spans="1:4" ht="62.4">
       <c r="B29" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D29" t="s">
         <v>75</v>
@@ -9635,13 +9991,13 @@
     </row>
     <row r="30" spans="1:4" ht="265.2">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D30" t="s">
         <v>75</v>
@@ -9652,7 +10008,7 @@
         <v>58</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D31" t="s">
         <v>72</v>
@@ -9660,10 +10016,10 @@
     </row>
     <row r="32" spans="1:4" ht="93.6">
       <c r="B32" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D32" t="s">
         <v>74</v>
@@ -9674,7 +10030,7 @@
         <v>54</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
         <v>67</v>
@@ -9685,7 +10041,7 @@
         <v>56</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
         <v>69</v>
@@ -9693,7 +10049,7 @@
     </row>
     <row r="35" spans="1:4" ht="62.4">
       <c r="A35" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>59</v>
@@ -9710,7 +10066,7 @@
         <v>58</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D36" t="s">
         <v>72</v>
@@ -9718,16 +10074,16 @@
     </row>
     <row r="37" spans="1:4" ht="62.4">
       <c r="A37" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="234">
@@ -9735,7 +10091,7 @@
         <v>48</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D38" t="s">
         <v>62</v>
@@ -9746,7 +10102,7 @@
         <v>50</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D39" t="s">
         <v>63</v>
@@ -9757,7 +10113,7 @@
         <v>54</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
         <v>67</v>
@@ -9768,7 +10124,7 @@
         <v>56</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D41" t="s">
         <v>69</v>
@@ -9776,10 +10132,10 @@
     </row>
     <row r="42" spans="1:4" ht="62.4">
       <c r="B42" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D42" t="s">
         <v>75</v>
@@ -9822,7 +10178,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -9897,7 +10253,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
+++ b/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wanho\Documents\kate_gait_subjective\gaitanalysersubjective\app\jsonfiles\excel\stance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B534366C-8CDF-4CC0-B45E-1BD148F61E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E45A6F-7111-422A-922C-596F5A486C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="258">
   <si>
     <t>label</t>
   </si>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>[42]</t>
-  </si>
-  <si>
-    <t>["other"]</t>
   </si>
   <si>
     <t>["rom"]</t>
@@ -1018,9 +1015,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">EXCESSIVE MUSCLE ACTIVITY: Increased ankle plantarflexor muscle activity during stance </t>
-  </si>
-  <si>
     <t>MMT ankle DF. Top tip: consider muscle strength with knee flexed and knee extended</t>
   </si>
   <si>
@@ -1318,10 +1312,16 @@
     <t>Hip extensors strengthening in gravity elimminated positions.</t>
   </si>
   <si>
-    <t>[5167,68]</t>
-  </si>
-  <si>
     <t>["knee_flexion","knee_extension"]</t>
+  </si>
+  <si>
+    <t>[51,67,68]</t>
+  </si>
+  <si>
+    <t>["sensation"]</t>
+  </si>
+  <si>
+    <t>["ex_mus_ac"]</t>
   </si>
 </sst>
 </file>
@@ -1826,7 +1826,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1850,10 +1850,10 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1">
@@ -1861,7 +1861,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -1882,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J2" s="2" t="str">
         <f>CONCATENATE("walking","_","Tx",A2)</f>
@@ -1894,7 +1894,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2">
         <v>3</v>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J3" s="2" t="str">
         <f t="shared" ref="J3:J60" si="0">CONCATENATE("walking","_","Tx",A3)</f>
@@ -1927,7 +1927,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J4" s="2" t="str">
         <f>CONCATENATE("walking","_","Tx",A4)</f>
@@ -1960,7 +1960,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -1981,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -1993,7 +1993,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -2014,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2026,7 +2026,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C7" s="2">
         <v>3</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2059,7 +2059,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2">
         <v>3</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2092,7 +2092,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="2">
         <v>3</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2125,7 +2125,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="2">
         <v>3</v>
@@ -2146,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2158,7 +2158,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="2">
         <v>3</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2191,7 +2191,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="0"/>
@@ -2224,7 +2224,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="0"/>
@@ -2257,7 +2257,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2">
         <v>3</v>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J14" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2290,7 +2290,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C15" s="2">
         <v>3</v>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J15" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2323,7 +2323,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J16" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2356,7 +2356,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J17" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2389,7 +2389,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J18" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2422,7 +2422,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
@@ -2443,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J19" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2455,7 +2455,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
@@ -2476,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J20" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2488,7 +2488,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J21" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2521,7 +2521,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J22" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2554,7 +2554,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" s="2">
         <v>2</v>
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J23" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2587,7 +2587,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J24" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2620,7 +2620,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" s="2">
         <v>2</v>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J25" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2653,7 +2653,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J26" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2686,7 +2686,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C27" s="2">
         <v>2</v>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J27" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2719,7 +2719,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C28" s="2">
         <v>3</v>
@@ -2740,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J28" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2752,7 +2752,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C29" s="2">
         <v>2</v>
@@ -2773,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J29" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2785,7 +2785,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30" s="2">
         <v>2</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J30" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2818,7 +2818,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31" s="2">
         <v>2</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J31" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2851,7 +2851,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" s="2">
         <v>3</v>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J32" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2884,7 +2884,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -2905,7 +2905,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J33" t="str">
         <f t="shared" si="0"/>
@@ -2917,7 +2917,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J34" t="str">
         <f t="shared" si="0"/>
@@ -2950,7 +2950,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J35" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2983,7 +2983,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J36" t="str">
         <f t="shared" si="0"/>
@@ -3016,7 +3016,7 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J37" t="str">
         <f t="shared" si="0"/>
@@ -3049,7 +3049,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J38" t="str">
         <f t="shared" si="0"/>
@@ -3082,7 +3082,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J39" t="str">
         <f t="shared" si="0"/>
@@ -3115,7 +3115,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J40" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3148,7 +3148,7 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -3169,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J41" t="str">
         <f t="shared" si="0"/>
@@ -3181,7 +3181,7 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -3202,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J42" t="str">
         <f t="shared" si="0"/>
@@ -3214,7 +3214,7 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J43" t="str">
         <f t="shared" si="0"/>
@@ -3247,7 +3247,7 @@
         <v>45</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J44" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3280,7 +3280,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3301,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J45" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3313,7 +3313,7 @@
         <v>47</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3334,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J46" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3346,7 +3346,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C47" s="2">
         <v>2</v>
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J47" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3379,7 +3379,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -3400,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J48" t="str">
         <f t="shared" si="0"/>
@@ -3412,7 +3412,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3433,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J49" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3445,7 +3445,7 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -3466,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J50" t="str">
         <f t="shared" si="0"/>
@@ -3478,7 +3478,7 @@
         <v>57</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C51" s="2">
         <v>2</v>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J51" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3511,7 +3511,7 @@
         <v>58</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C52" s="2">
         <v>2</v>
@@ -3532,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J52" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3544,7 +3544,7 @@
         <v>59</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C53" s="2">
         <v>3</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J53" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3577,7 +3577,7 @@
         <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J54" t="str">
         <f t="shared" si="0"/>
@@ -3610,7 +3610,7 @@
         <v>61</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C55" s="2">
         <v>3</v>
@@ -3631,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J55" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3643,7 +3643,7 @@
         <v>62</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C56" s="2">
         <v>2</v>
@@ -3664,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J56" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3676,7 +3676,7 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57">
         <v>3</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J57" t="str">
         <f t="shared" si="0"/>
@@ -3709,7 +3709,7 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J58" t="str">
         <f t="shared" si="0"/>
@@ -3742,7 +3742,7 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J59" t="str">
         <f t="shared" si="0"/>
@@ -3775,7 +3775,7 @@
         <v>66</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C60" s="2">
         <v>2</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J60" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3808,7 +3808,7 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J61" t="str">
         <f t="shared" ref="J61" si="1">CONCATENATE("walking","_","Tx",A61)</f>
@@ -3841,7 +3841,7 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J62" t="str">
         <f t="shared" ref="J62" si="2">CONCATENATE("walking","_","Tx",A62)</f>
@@ -3888,13 +3888,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3902,10 +3902,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3913,10 +3913,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3924,10 +3924,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3935,10 +3935,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3946,10 +3946,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3957,10 +3957,10 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3968,10 +3968,10 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3979,10 +3979,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3990,10 +3990,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -4004,18 +4004,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:IA30"/>
+  <dimension ref="A1:IA29"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.6"/>
   <cols>
     <col min="2" max="2" width="60.8984375" customWidth="1"/>
-    <col min="3" max="3" width="6.19921875" customWidth="1"/>
-    <col min="4" max="4" width="3.59765625" customWidth="1"/>
+    <col min="3" max="3" width="5.69921875" customWidth="1"/>
+    <col min="4" max="4" width="8.3984375" customWidth="1"/>
     <col min="5" max="5" width="57.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:235">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
         <v>7</v>
@@ -4038,19 +4038,19 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -4287,16 +4287,16 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
@@ -4536,19 +4536,19 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>256</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -4785,19 +4785,19 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -5034,16 +5034,16 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
@@ -5283,16 +5283,16 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
@@ -5532,16 +5532,16 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E8" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
@@ -5781,19 +5781,19 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9"/>
       <c r="H9"/>
@@ -6030,16 +6030,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
@@ -6279,19 +6279,19 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11"/>
       <c r="H11"/>
@@ -6528,16 +6528,16 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
@@ -6777,19 +6777,19 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G13"/>
       <c r="H13"/>
@@ -7026,19 +7026,19 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
         <v>19</v>
-      </c>
-      <c r="F14" t="s">
-        <v>20</v>
       </c>
       <c r="G14"/>
       <c r="H14"/>
@@ -7275,16 +7275,16 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
@@ -7524,19 +7524,19 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16"/>
       <c r="H16"/>
@@ -7773,16 +7773,16 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -8022,16 +8022,16 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
@@ -8271,19 +8271,19 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G19"/>
       <c r="H19"/>
@@ -8520,16 +8520,16 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
@@ -8769,16 +8769,16 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -9018,19 +9018,19 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="G22"/>
       <c r="H22"/>
@@ -9267,19 +9267,19 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:235">
@@ -9287,19 +9287,19 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:235">
@@ -9307,19 +9307,19 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" spans="1:235">
@@ -9327,19 +9327,19 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" spans="1:235">
@@ -9347,302 +9347,282 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:235">
       <c r="A28">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E28" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:235">
-      <c r="A29">
-        <v>29</v>
-      </c>
-      <c r="B29" t="s">
-        <v>242</v>
-      </c>
-      <c r="C29" t="s">
-        <v>125</v>
-      </c>
-      <c r="D29" t="s">
-        <v>72</v>
-      </c>
-      <c r="E29" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:235" s="2" customFormat="1">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30"/>
-      <c r="M30"/>
-      <c r="N30"/>
-      <c r="O30"/>
-      <c r="P30"/>
-      <c r="Q30"/>
-      <c r="R30"/>
-      <c r="S30"/>
-      <c r="T30"/>
-      <c r="U30"/>
-      <c r="V30"/>
-      <c r="W30"/>
-      <c r="X30"/>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AA30"/>
-      <c r="AB30"/>
-      <c r="AC30"/>
-      <c r="AD30"/>
-      <c r="AE30"/>
-      <c r="AF30"/>
-      <c r="AG30"/>
-      <c r="AH30"/>
-      <c r="AI30"/>
-      <c r="AJ30"/>
-      <c r="AK30"/>
-      <c r="AL30"/>
-      <c r="AM30"/>
-      <c r="AN30"/>
-      <c r="AO30"/>
-      <c r="AP30"/>
-      <c r="AQ30"/>
-      <c r="AR30"/>
-      <c r="AS30"/>
-      <c r="AT30"/>
-      <c r="AU30"/>
-      <c r="AV30"/>
-      <c r="AW30"/>
-      <c r="AX30"/>
-      <c r="AY30"/>
-      <c r="AZ30"/>
-      <c r="BA30"/>
-      <c r="BB30"/>
-      <c r="BC30"/>
-      <c r="BD30"/>
-      <c r="BE30"/>
-      <c r="BF30"/>
-      <c r="BG30"/>
-      <c r="BH30"/>
-      <c r="BI30"/>
-      <c r="BJ30"/>
-      <c r="BK30"/>
-      <c r="BL30"/>
-      <c r="BM30"/>
-      <c r="BN30"/>
-      <c r="BO30"/>
-      <c r="BP30"/>
-      <c r="BQ30"/>
-      <c r="BR30"/>
-      <c r="BS30"/>
-      <c r="BT30"/>
-      <c r="BU30"/>
-      <c r="BV30"/>
-      <c r="BW30"/>
-      <c r="BX30"/>
-      <c r="BY30"/>
-      <c r="BZ30"/>
-      <c r="CA30"/>
-      <c r="CB30"/>
-      <c r="CC30"/>
-      <c r="CD30"/>
-      <c r="CE30"/>
-      <c r="CF30"/>
-      <c r="CG30"/>
-      <c r="CH30"/>
-      <c r="CI30"/>
-      <c r="CJ30"/>
-      <c r="CK30"/>
-      <c r="CL30"/>
-      <c r="CM30"/>
-      <c r="CN30"/>
-      <c r="CO30"/>
-      <c r="CP30"/>
-      <c r="CQ30"/>
-      <c r="CR30"/>
-      <c r="CS30"/>
-      <c r="CT30"/>
-      <c r="CU30"/>
-      <c r="CV30"/>
-      <c r="CW30"/>
-      <c r="CX30"/>
-      <c r="CY30"/>
-      <c r="CZ30"/>
-      <c r="DA30"/>
-      <c r="DB30"/>
-      <c r="DC30"/>
-      <c r="DD30"/>
-      <c r="DE30"/>
-      <c r="DF30"/>
-      <c r="DG30"/>
-      <c r="DH30"/>
-      <c r="DI30"/>
-      <c r="DJ30"/>
-      <c r="DK30"/>
-      <c r="DL30"/>
-      <c r="DM30"/>
-      <c r="DN30"/>
-      <c r="DO30"/>
-      <c r="DP30"/>
-      <c r="DQ30"/>
-      <c r="DR30"/>
-      <c r="DS30"/>
-      <c r="DT30"/>
-      <c r="DU30"/>
-      <c r="DV30"/>
-      <c r="DW30"/>
-      <c r="DX30"/>
-      <c r="DY30"/>
-      <c r="DZ30"/>
-      <c r="EA30"/>
-      <c r="EB30"/>
-      <c r="EC30"/>
-      <c r="ED30"/>
-      <c r="EE30"/>
-      <c r="EF30"/>
-      <c r="EG30"/>
-      <c r="EH30"/>
-      <c r="EI30"/>
-      <c r="EJ30"/>
-      <c r="EK30"/>
-      <c r="EL30"/>
-      <c r="EM30"/>
-      <c r="EN30"/>
-      <c r="EO30"/>
-      <c r="EP30"/>
-      <c r="EQ30"/>
-      <c r="ER30"/>
-      <c r="ES30"/>
-      <c r="ET30"/>
-      <c r="EU30"/>
-      <c r="EV30"/>
-      <c r="EW30"/>
-      <c r="EX30"/>
-      <c r="EY30"/>
-      <c r="EZ30"/>
-      <c r="FA30"/>
-      <c r="FB30"/>
-      <c r="FC30"/>
-      <c r="FD30"/>
-      <c r="FE30"/>
-      <c r="FF30"/>
-      <c r="FG30"/>
-      <c r="FH30"/>
-      <c r="FI30"/>
-      <c r="FJ30"/>
-      <c r="FK30"/>
-      <c r="FL30"/>
-      <c r="FM30"/>
-      <c r="FN30"/>
-      <c r="FO30"/>
-      <c r="FP30"/>
-      <c r="FQ30"/>
-      <c r="FR30"/>
-      <c r="FS30"/>
-      <c r="FT30"/>
-      <c r="FU30"/>
-      <c r="FV30"/>
-      <c r="FW30"/>
-      <c r="FX30"/>
-      <c r="FY30"/>
-      <c r="FZ30"/>
-      <c r="GA30"/>
-      <c r="GB30"/>
-      <c r="GC30"/>
-      <c r="GD30"/>
-      <c r="GE30"/>
-      <c r="GF30"/>
-      <c r="GG30"/>
-      <c r="GH30"/>
-      <c r="GI30"/>
-      <c r="GJ30"/>
-      <c r="GK30"/>
-      <c r="GL30"/>
-      <c r="GM30"/>
-      <c r="GN30"/>
-      <c r="GO30"/>
-      <c r="GP30"/>
-      <c r="GQ30"/>
-      <c r="GR30"/>
-      <c r="GS30"/>
-      <c r="GT30"/>
-      <c r="GU30"/>
-      <c r="GV30"/>
-      <c r="GW30"/>
-      <c r="GX30"/>
-      <c r="GY30"/>
-      <c r="GZ30"/>
-      <c r="HA30"/>
-      <c r="HB30"/>
-      <c r="HC30"/>
-      <c r="HD30"/>
-      <c r="HE30"/>
-      <c r="HF30"/>
-      <c r="HG30"/>
-      <c r="HH30"/>
-      <c r="HI30"/>
-      <c r="HJ30"/>
-      <c r="HK30"/>
-      <c r="HL30"/>
-      <c r="HM30"/>
-      <c r="HN30"/>
-      <c r="HO30"/>
-      <c r="HP30"/>
-      <c r="HQ30"/>
-      <c r="HR30"/>
-      <c r="HS30"/>
-      <c r="HT30"/>
-      <c r="HU30"/>
-      <c r="HV30"/>
-      <c r="HW30"/>
-      <c r="HX30"/>
-      <c r="HY30"/>
-      <c r="HZ30"/>
-      <c r="IA30"/>
+    <row r="29" spans="1:235" s="2" customFormat="1">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+      <c r="S29"/>
+      <c r="T29"/>
+      <c r="U29"/>
+      <c r="V29"/>
+      <c r="W29"/>
+      <c r="X29"/>
+      <c r="Y29"/>
+      <c r="Z29"/>
+      <c r="AA29"/>
+      <c r="AB29"/>
+      <c r="AC29"/>
+      <c r="AD29"/>
+      <c r="AE29"/>
+      <c r="AF29"/>
+      <c r="AG29"/>
+      <c r="AH29"/>
+      <c r="AI29"/>
+      <c r="AJ29"/>
+      <c r="AK29"/>
+      <c r="AL29"/>
+      <c r="AM29"/>
+      <c r="AN29"/>
+      <c r="AO29"/>
+      <c r="AP29"/>
+      <c r="AQ29"/>
+      <c r="AR29"/>
+      <c r="AS29"/>
+      <c r="AT29"/>
+      <c r="AU29"/>
+      <c r="AV29"/>
+      <c r="AW29"/>
+      <c r="AX29"/>
+      <c r="AY29"/>
+      <c r="AZ29"/>
+      <c r="BA29"/>
+      <c r="BB29"/>
+      <c r="BC29"/>
+      <c r="BD29"/>
+      <c r="BE29"/>
+      <c r="BF29"/>
+      <c r="BG29"/>
+      <c r="BH29"/>
+      <c r="BI29"/>
+      <c r="BJ29"/>
+      <c r="BK29"/>
+      <c r="BL29"/>
+      <c r="BM29"/>
+      <c r="BN29"/>
+      <c r="BO29"/>
+      <c r="BP29"/>
+      <c r="BQ29"/>
+      <c r="BR29"/>
+      <c r="BS29"/>
+      <c r="BT29"/>
+      <c r="BU29"/>
+      <c r="BV29"/>
+      <c r="BW29"/>
+      <c r="BX29"/>
+      <c r="BY29"/>
+      <c r="BZ29"/>
+      <c r="CA29"/>
+      <c r="CB29"/>
+      <c r="CC29"/>
+      <c r="CD29"/>
+      <c r="CE29"/>
+      <c r="CF29"/>
+      <c r="CG29"/>
+      <c r="CH29"/>
+      <c r="CI29"/>
+      <c r="CJ29"/>
+      <c r="CK29"/>
+      <c r="CL29"/>
+      <c r="CM29"/>
+      <c r="CN29"/>
+      <c r="CO29"/>
+      <c r="CP29"/>
+      <c r="CQ29"/>
+      <c r="CR29"/>
+      <c r="CS29"/>
+      <c r="CT29"/>
+      <c r="CU29"/>
+      <c r="CV29"/>
+      <c r="CW29"/>
+      <c r="CX29"/>
+      <c r="CY29"/>
+      <c r="CZ29"/>
+      <c r="DA29"/>
+      <c r="DB29"/>
+      <c r="DC29"/>
+      <c r="DD29"/>
+      <c r="DE29"/>
+      <c r="DF29"/>
+      <c r="DG29"/>
+      <c r="DH29"/>
+      <c r="DI29"/>
+      <c r="DJ29"/>
+      <c r="DK29"/>
+      <c r="DL29"/>
+      <c r="DM29"/>
+      <c r="DN29"/>
+      <c r="DO29"/>
+      <c r="DP29"/>
+      <c r="DQ29"/>
+      <c r="DR29"/>
+      <c r="DS29"/>
+      <c r="DT29"/>
+      <c r="DU29"/>
+      <c r="DV29"/>
+      <c r="DW29"/>
+      <c r="DX29"/>
+      <c r="DY29"/>
+      <c r="DZ29"/>
+      <c r="EA29"/>
+      <c r="EB29"/>
+      <c r="EC29"/>
+      <c r="ED29"/>
+      <c r="EE29"/>
+      <c r="EF29"/>
+      <c r="EG29"/>
+      <c r="EH29"/>
+      <c r="EI29"/>
+      <c r="EJ29"/>
+      <c r="EK29"/>
+      <c r="EL29"/>
+      <c r="EM29"/>
+      <c r="EN29"/>
+      <c r="EO29"/>
+      <c r="EP29"/>
+      <c r="EQ29"/>
+      <c r="ER29"/>
+      <c r="ES29"/>
+      <c r="ET29"/>
+      <c r="EU29"/>
+      <c r="EV29"/>
+      <c r="EW29"/>
+      <c r="EX29"/>
+      <c r="EY29"/>
+      <c r="EZ29"/>
+      <c r="FA29"/>
+      <c r="FB29"/>
+      <c r="FC29"/>
+      <c r="FD29"/>
+      <c r="FE29"/>
+      <c r="FF29"/>
+      <c r="FG29"/>
+      <c r="FH29"/>
+      <c r="FI29"/>
+      <c r="FJ29"/>
+      <c r="FK29"/>
+      <c r="FL29"/>
+      <c r="FM29"/>
+      <c r="FN29"/>
+      <c r="FO29"/>
+      <c r="FP29"/>
+      <c r="FQ29"/>
+      <c r="FR29"/>
+      <c r="FS29"/>
+      <c r="FT29"/>
+      <c r="FU29"/>
+      <c r="FV29"/>
+      <c r="FW29"/>
+      <c r="FX29"/>
+      <c r="FY29"/>
+      <c r="FZ29"/>
+      <c r="GA29"/>
+      <c r="GB29"/>
+      <c r="GC29"/>
+      <c r="GD29"/>
+      <c r="GE29"/>
+      <c r="GF29"/>
+      <c r="GG29"/>
+      <c r="GH29"/>
+      <c r="GI29"/>
+      <c r="GJ29"/>
+      <c r="GK29"/>
+      <c r="GL29"/>
+      <c r="GM29"/>
+      <c r="GN29"/>
+      <c r="GO29"/>
+      <c r="GP29"/>
+      <c r="GQ29"/>
+      <c r="GR29"/>
+      <c r="GS29"/>
+      <c r="GT29"/>
+      <c r="GU29"/>
+      <c r="GV29"/>
+      <c r="GW29"/>
+      <c r="GX29"/>
+      <c r="GY29"/>
+      <c r="GZ29"/>
+      <c r="HA29"/>
+      <c r="HB29"/>
+      <c r="HC29"/>
+      <c r="HD29"/>
+      <c r="HE29"/>
+      <c r="HF29"/>
+      <c r="HG29"/>
+      <c r="HH29"/>
+      <c r="HI29"/>
+      <c r="HJ29"/>
+      <c r="HK29"/>
+      <c r="HL29"/>
+      <c r="HM29"/>
+      <c r="HN29"/>
+      <c r="HO29"/>
+      <c r="HP29"/>
+      <c r="HQ29"/>
+      <c r="HR29"/>
+      <c r="HS29"/>
+      <c r="HT29"/>
+      <c r="HU29"/>
+      <c r="HV29"/>
+      <c r="HW29"/>
+      <c r="HX29"/>
+      <c r="HY29"/>
+      <c r="HZ29"/>
+      <c r="IA29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="B1 D1 F1 F4 E5:F5 E7:F7 F8 E10:F10 E11:F11 E12:F12 E13:F13 F14 E15:F15 E16 E17 E18:F18 E19:F19 E20 F3" numberStoredAsText="1"/>
+    <ignoredError sqref="B1 D1 F1 E5:F5 E7:F7 F8 E10:F10 E11:F11 E12:F12 E13:F13 F14 E15:F15 E16 E17 E18:F18 E19:F19 E20" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9665,480 +9645,480 @@
     </row>
     <row r="2" spans="1:4" ht="78">
       <c r="A2" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="156">
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="31.2">
       <c r="B4" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="187.2">
       <c r="B5" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="62.4">
       <c r="B6" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="46.8">
       <c r="A7" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="187.2">
       <c r="B8" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="234">
       <c r="B9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="249.6">
       <c r="B10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="187.2">
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="156">
       <c r="B12" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="46.8">
       <c r="A13" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="374.4">
       <c r="B14" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="327.60000000000002">
       <c r="B15" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="156">
       <c r="A16" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="109.2">
       <c r="B17" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="156">
       <c r="B18" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="234">
       <c r="A19" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="187.2">
       <c r="B20" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="171.6">
       <c r="B21" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="187.2">
       <c r="A22" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="234">
       <c r="B23" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="187.2">
       <c r="B24" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="31.2">
       <c r="B25" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="31.2">
       <c r="B26" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="46.8">
       <c r="B27" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="109.2">
       <c r="B28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D28" t="s">
         <v>60</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D28" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="62.4">
       <c r="B29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="265.2">
       <c r="A30" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="93.6">
       <c r="B31" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="93.6">
       <c r="B32" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="187.2">
       <c r="B33" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="31.2">
       <c r="B34" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="62.4">
       <c r="A35" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="93.6">
       <c r="B36" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="62.4">
       <c r="A37" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="234">
       <c r="B38" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="234">
       <c r="B39" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="187.2">
       <c r="B40" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="31.2">
       <c r="B41" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="62.4">
       <c r="B42" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="D42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -10158,52 +10138,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -10213,47 +10193,47 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
+++ b/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wanho\Documents\kate_gait_subjective\gaitanalysersubjective\app\jsonfiles\excel\stance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E45A6F-7111-422A-922C-596F5A486C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A18BCB-04EE-4D8B-BCE1-B7F10F17D716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="264">
   <si>
     <t>label</t>
   </si>
@@ -349,9 +349,6 @@
   </si>
   <si>
     <t>Assess ability to rapidly plantarflex ankle (heel raise, single leg heel raise)</t>
-  </si>
-  <si>
-    <t>MMT knee flexors</t>
   </si>
   <si>
     <t>Assess ability to control knee flexion/extension on landing/heel strike</t>
@@ -1015,9 +1012,6 @@
     </r>
   </si>
   <si>
-    <t>MMT ankle DF. Top tip: consider muscle strength with knee flexed and knee extended</t>
-  </si>
-  <si>
     <t>Screen if the person is able to DF with knee moving from flexion into extension</t>
   </si>
   <si>
@@ -1101,19 +1095,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> ability to maintain knee and hip extension whilst shifting weight on the leg and stepping</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">MMT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF92D050"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>knee flexors</t>
     </r>
   </si>
   <si>
@@ -1322,6 +1303,53 @@
   </si>
   <si>
     <t>["ex_mus_ac"]</t>
+  </si>
+  <si>
+    <t>MMT ankle DF. Top tip: consider muscle strength with knee flexed and knee extended. Please classify strength level as below based on your assessment.</t>
+  </si>
+  <si>
+    <t>MMT ankle plantarflexors.  Please classify strength level as below based on your assessment.</t>
+  </si>
+  <si>
+    <t>MMT knee flexors.  Please classify strength level as below based on your assessment.</t>
+  </si>
+  <si>
+    <t>MMT knee extensors.  Please classify strength level as below based on your assessment.</t>
+  </si>
+  <si>
+    <t>MMT hip extensors.  Please classify strength level as below based on your assessment.</t>
+  </si>
+  <si>
+    <t>MMT hip flexors.  Please classify strength level as below based on your assessment.</t>
+  </si>
+  <si>
+    <t>MMT of hip abductors.  Please classify strength level as below based on your assessment.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MMT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF92D050"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>knee flexors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.  Please classify strength level as below based on your assessment.</t>
+    </r>
+  </si>
+  <si>
+    <t>MMT hip adductors.  Please classify strength level as below based on your assessment.</t>
   </si>
 </sst>
 </file>
@@ -1826,7 +1854,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1850,10 +1878,10 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1">
@@ -1861,7 +1889,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -1882,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J2" s="2" t="str">
         <f>CONCATENATE("walking","_","Tx",A2)</f>
@@ -1894,7 +1922,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2">
         <v>3</v>
@@ -1915,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J3" s="2" t="str">
         <f t="shared" ref="J3:J60" si="0">CONCATENATE("walking","_","Tx",A3)</f>
@@ -1927,7 +1955,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -1948,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J4" s="2" t="str">
         <f>CONCATENATE("walking","_","Tx",A4)</f>
@@ -1960,7 +1988,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -1981,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -1993,7 +2021,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -2014,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2026,7 +2054,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C7" s="2">
         <v>3</v>
@@ -2047,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2059,7 +2087,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2">
         <v>3</v>
@@ -2080,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2092,7 +2120,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="2">
         <v>3</v>
@@ -2113,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2125,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" s="2">
         <v>3</v>
@@ -2146,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2158,7 +2186,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="2">
         <v>3</v>
@@ -2179,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2191,7 +2219,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -2212,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="0"/>
@@ -2224,7 +2252,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -2245,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="0"/>
@@ -2257,7 +2285,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2">
         <v>3</v>
@@ -2278,7 +2306,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J14" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2290,7 +2318,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C15" s="2">
         <v>3</v>
@@ -2311,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J15" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2323,7 +2351,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
@@ -2344,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J16" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2356,7 +2384,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
@@ -2377,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J17" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2389,7 +2417,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
@@ -2410,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J18" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2422,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
@@ -2443,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J19" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2455,7 +2483,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
@@ -2476,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J20" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2488,7 +2516,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
@@ -2509,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J21" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2521,7 +2549,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -2542,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J22" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2554,7 +2582,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" s="2">
         <v>2</v>
@@ -2575,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J23" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2587,7 +2615,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
@@ -2608,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J24" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2620,7 +2648,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C25" s="2">
         <v>2</v>
@@ -2641,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J25" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2653,7 +2681,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
@@ -2674,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J26" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2686,7 +2714,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C27" s="2">
         <v>2</v>
@@ -2707,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J27" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2719,7 +2747,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" s="2">
         <v>3</v>
@@ -2740,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J28" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2752,7 +2780,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C29" s="2">
         <v>2</v>
@@ -2773,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J29" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2785,7 +2813,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C30" s="2">
         <v>2</v>
@@ -2806,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J30" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2818,7 +2846,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C31" s="2">
         <v>2</v>
@@ -2839,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J31" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2851,7 +2879,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C32" s="2">
         <v>3</v>
@@ -2872,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J32" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2884,7 +2912,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -2905,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J33" t="str">
         <f t="shared" si="0"/>
@@ -2917,7 +2945,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2938,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J34" t="str">
         <f t="shared" si="0"/>
@@ -2950,7 +2978,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -2971,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J35" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2983,7 +3011,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -3004,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J36" t="str">
         <f t="shared" si="0"/>
@@ -3016,7 +3044,7 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -3037,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J37" t="str">
         <f t="shared" si="0"/>
@@ -3049,7 +3077,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -3070,7 +3098,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J38" t="str">
         <f t="shared" si="0"/>
@@ -3082,7 +3110,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -3103,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J39" t="str">
         <f t="shared" si="0"/>
@@ -3115,7 +3143,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3136,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J40" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3148,7 +3176,7 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -3169,7 +3197,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J41" t="str">
         <f t="shared" si="0"/>
@@ -3181,7 +3209,7 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -3202,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J42" t="str">
         <f t="shared" si="0"/>
@@ -3214,7 +3242,7 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -3235,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J43" t="str">
         <f t="shared" si="0"/>
@@ -3247,7 +3275,7 @@
         <v>45</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -3268,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J44" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3280,7 +3308,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3301,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J45" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3313,7 +3341,7 @@
         <v>47</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3334,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J46" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3346,7 +3374,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C47" s="2">
         <v>2</v>
@@ -3367,7 +3395,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J47" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3379,7 +3407,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -3400,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J48" t="str">
         <f t="shared" si="0"/>
@@ -3412,7 +3440,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3433,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J49" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3445,7 +3473,7 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -3466,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J50" t="str">
         <f t="shared" si="0"/>
@@ -3478,7 +3506,7 @@
         <v>57</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C51" s="2">
         <v>2</v>
@@ -3499,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J51" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3511,7 +3539,7 @@
         <v>58</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C52" s="2">
         <v>2</v>
@@ -3532,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J52" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3544,7 +3572,7 @@
         <v>59</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C53" s="2">
         <v>3</v>
@@ -3565,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J53" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3577,7 +3605,7 @@
         <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -3598,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J54" t="str">
         <f t="shared" si="0"/>
@@ -3610,7 +3638,7 @@
         <v>61</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C55" s="2">
         <v>3</v>
@@ -3631,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J55" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3643,7 +3671,7 @@
         <v>62</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C56" s="2">
         <v>2</v>
@@ -3664,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J56" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3676,7 +3704,7 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C57">
         <v>3</v>
@@ -3697,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J57" t="str">
         <f t="shared" si="0"/>
@@ -3709,7 +3737,7 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -3730,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J58" t="str">
         <f t="shared" si="0"/>
@@ -3742,7 +3770,7 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -3763,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J59" t="str">
         <f t="shared" si="0"/>
@@ -3775,7 +3803,7 @@
         <v>66</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C60" s="2">
         <v>2</v>
@@ -3796,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J60" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3808,7 +3836,7 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -3829,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J61" t="str">
         <f t="shared" ref="J61" si="1">CONCATENATE("walking","_","Tx",A61)</f>
@@ -3841,7 +3869,7 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -3862,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J62" t="str">
         <f t="shared" ref="J62" si="2">CONCATENATE("walking","_","Tx",A62)</f>
@@ -3888,13 +3916,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3905,7 +3933,7 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3916,7 +3944,7 @@
         <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3924,10 +3952,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3938,7 +3966,7 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3949,7 +3977,7 @@
         <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3957,10 +3985,10 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3971,7 +3999,7 @@
         <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3982,7 +4010,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3990,10 +4018,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -4009,13 +4037,13 @@
   <cols>
     <col min="2" max="2" width="60.8984375" customWidth="1"/>
     <col min="3" max="3" width="5.69921875" customWidth="1"/>
-    <col min="4" max="4" width="8.3984375" customWidth="1"/>
+    <col min="4" max="4" width="54.69921875" customWidth="1"/>
     <col min="5" max="5" width="57.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:235">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s">
         <v>7</v>
@@ -4038,13 +4066,13 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -4287,16 +4315,16 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
@@ -4536,19 +4564,19 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -4785,10 +4813,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
         <v>60</v>
@@ -5034,16 +5062,16 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>256</v>
       </c>
       <c r="E6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
@@ -5283,13 +5311,13 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -5532,16 +5560,16 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
@@ -5781,16 +5809,16 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>256</v>
       </c>
       <c r="E9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F9" t="s">
         <v>19</v>
@@ -6030,10 +6058,10 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D10" t="s">
         <v>63</v>
@@ -6279,13 +6307,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>257</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -6528,13 +6556,13 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E12" t="s">
         <v>20</v>
@@ -6777,10 +6805,10 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
         <v>60</v>
@@ -7026,13 +7054,13 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>258</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -7275,13 +7303,13 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -7524,13 +7552,13 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C16" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>259</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
@@ -7773,13 +7801,13 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>260</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
@@ -8022,13 +8050,13 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E18" t="s">
         <v>21</v>
@@ -8271,10 +8299,10 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D19" t="s">
         <v>60</v>
@@ -8520,13 +8548,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>261</v>
       </c>
       <c r="E20" t="s">
         <v>23</v>
@@ -8769,13 +8797,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="E21" t="s">
         <v>20</v>
@@ -9018,19 +9046,19 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s">
         <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G22"/>
       <c r="H22"/>
@@ -9267,19 +9295,19 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24" spans="1:235">
@@ -9287,16 +9315,16 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
+        <v>263</v>
       </c>
       <c r="E24" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -9307,19 +9335,19 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E25" t="s">
         <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" spans="1:235">
@@ -9327,19 +9355,19 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E26" t="s">
         <v>20</v>
       </c>
       <c r="F26" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:235">
@@ -9347,19 +9375,19 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:235">
@@ -9367,13 +9395,13 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>261</v>
       </c>
       <c r="E28" t="s">
         <v>23</v>
@@ -9645,46 +9673,46 @@
     </row>
     <row r="2" spans="1:4" ht="78">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="156">
       <c r="B3" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="31.2">
       <c r="B4" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="187.2">
       <c r="B5" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
         <v>60</v>
@@ -9692,35 +9720,35 @@
     </row>
     <row r="6" spans="1:4" ht="62.4">
       <c r="B6" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="46.8">
       <c r="A7" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="187.2">
       <c r="B8" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
@@ -9731,7 +9759,7 @@
         <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
         <v>61</v>
@@ -9742,10 +9770,10 @@
         <v>48</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="187.2">
@@ -9753,35 +9781,35 @@
         <v>53</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="156">
       <c r="B12" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="46.8">
       <c r="A13" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="374.4">
@@ -9789,7 +9817,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
@@ -9800,7 +9828,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D15" t="s">
         <v>63</v>
@@ -9808,49 +9836,49 @@
     </row>
     <row r="16" spans="1:4" ht="156">
       <c r="A16" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="109.2">
       <c r="B17" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="156">
       <c r="B18" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="234">
       <c r="A19" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D19" t="s">
         <v>61</v>
@@ -9861,10 +9889,10 @@
         <v>53</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="171.6">
@@ -9872,21 +9900,21 @@
         <v>54</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="187.2">
       <c r="A22" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D22" t="s">
         <v>60</v>
@@ -9897,7 +9925,7 @@
         <v>47</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D23" t="s">
         <v>61</v>
@@ -9908,10 +9936,10 @@
         <v>53</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="31.2">
@@ -9919,10 +9947,10 @@
         <v>55</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="31.2">
@@ -9930,10 +9958,10 @@
         <v>56</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="46.8">
@@ -9941,10 +9969,10 @@
         <v>58</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="109.2">
@@ -9952,7 +9980,7 @@
         <v>59</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D28" t="s">
         <v>60</v>
@@ -9960,27 +9988,27 @@
     </row>
     <row r="29" spans="1:4" ht="62.4">
       <c r="B29" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="265.2">
       <c r="A30" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="93.6">
@@ -9988,21 +10016,21 @@
         <v>57</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="93.6">
       <c r="B32" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="187.2">
@@ -10010,10 +10038,10 @@
         <v>53</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="31.2">
@@ -10021,24 +10049,24 @@
         <v>55</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="62.4">
       <c r="A35" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="93.6">
@@ -10046,24 +10074,24 @@
         <v>57</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="62.4">
       <c r="A37" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="234">
@@ -10071,7 +10099,7 @@
         <v>47</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s">
         <v>61</v>
@@ -10082,7 +10110,7 @@
         <v>49</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D39" t="s">
         <v>62</v>
@@ -10093,10 +10121,10 @@
         <v>53</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="31.2">
@@ -10104,21 +10132,21 @@
         <v>55</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="62.4">
       <c r="B42" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -10158,7 +10186,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -10233,7 +10261,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
+++ b/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wanho\Documents\kate_gait_subjective\gaitanalysersubjective\app\jsonfiles\excel\stance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A18BCB-04EE-4D8B-BCE1-B7F10F17D716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2254A110-4A0C-4C82-AED9-73A036F68E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="treatments" sheetId="1" r:id="rId1"/>

--- a/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
+++ b/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wanho\Documents\kate_gait_subjective\gaitanalysersubjective\app\jsonfiles\excel\stance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2254A110-4A0C-4C82-AED9-73A036F68E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A78BC11-5C6C-4B5F-886E-D09397AC9D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="treatments" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="265">
   <si>
     <t>label</t>
   </si>
@@ -531,9 +531,6 @@
     <t>[39,40]</t>
   </si>
   <si>
-    <t>[4,9,10]</t>
-  </si>
-  <si>
     <t>Decreased sensation of the foot/ankle and/or knee</t>
   </si>
   <si>
@@ -652,9 +649,6 @@
     <t>Part practice: stepping intact leg forward and up onto a block to promote hip extension.</t>
   </si>
   <si>
-    <t>[4,5,6,7,14,27]</t>
-  </si>
-  <si>
     <t>Whole practice walking: emphasising heel strike at initial contact_x000D_
 _x000D_
 Whole practice walking: use of footprints/markers for heel contact overground/treadmill_x000D_
@@ -717,16 +711,10 @@
     <t>[20,23,24]</t>
   </si>
   <si>
-    <t>[6,14,15]</t>
-  </si>
-  <si>
     <t>Hip flexion strengthening in sitting or lying with a focus on the eccentric phase</t>
   </si>
   <si>
     <t>[33,64]</t>
-  </si>
-  <si>
-    <t>[5,6,14,16,17,18,19,23]</t>
   </si>
   <si>
     <t>[65,66]</t>
@@ -1350,6 +1338,21 @@
   </si>
   <si>
     <t>MMT hip adductors.  Please classify strength level as below based on your assessment.</t>
+  </si>
+  <si>
+    <t>[4,5,6,9,7,14,27]</t>
+  </si>
+  <si>
+    <t>[6,9,14,15]</t>
+  </si>
+  <si>
+    <t>[6,4,9,10]</t>
+  </si>
+  <si>
+    <t>STRENGTH: Decreased strength hip flexors (concentric)</t>
+  </si>
+  <si>
+    <t>[5,6,9,14,16,17,30,18,19,23]</t>
   </si>
 </sst>
 </file>
@@ -1878,10 +1881,10 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1">
@@ -1910,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J2" s="2" t="str">
         <f>CONCATENATE("walking","_","Tx",A2)</f>
@@ -1943,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J3" s="2" t="str">
         <f t="shared" ref="J3:J60" si="0">CONCATENATE("walking","_","Tx",A3)</f>
@@ -1976,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J4" s="2" t="str">
         <f>CONCATENATE("walking","_","Tx",A4)</f>
@@ -2009,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2021,7 +2024,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -2042,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2054,7 +2057,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C7" s="2">
         <v>3</v>
@@ -2075,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2108,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2141,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2174,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2207,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2240,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="0"/>
@@ -2252,7 +2255,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -2273,7 +2276,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="0"/>
@@ -2285,7 +2288,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2">
         <v>3</v>
@@ -2306,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J14" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2318,7 +2321,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C15" s="2">
         <v>3</v>
@@ -2339,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J15" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2351,7 +2354,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
@@ -2372,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J16" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2405,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J17" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2438,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J18" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2450,7 +2453,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
@@ -2471,7 +2474,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J19" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2483,7 +2486,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
@@ -2504,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J20" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2537,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J21" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2549,7 +2552,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -2570,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J22" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2603,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J23" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2615,7 +2618,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
@@ -2636,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J24" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2669,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J25" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2681,7 +2684,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
@@ -2702,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J26" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2714,7 +2717,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C27" s="2">
         <v>2</v>
@@ -2735,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J27" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2768,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J28" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2801,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J29" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2834,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J30" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2867,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J31" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2900,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J32" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2912,7 +2915,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -2933,7 +2936,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J33" t="str">
         <f t="shared" si="0"/>
@@ -2966,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J34" t="str">
         <f t="shared" si="0"/>
@@ -2978,7 +2981,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -2999,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J35" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3011,7 +3014,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -3032,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J36" t="str">
         <f t="shared" si="0"/>
@@ -3065,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J37" t="str">
         <f t="shared" si="0"/>
@@ -3077,7 +3080,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -3098,7 +3101,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J38" t="str">
         <f t="shared" si="0"/>
@@ -3131,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J39" t="str">
         <f t="shared" si="0"/>
@@ -3164,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J40" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3197,7 +3200,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J41" t="str">
         <f t="shared" si="0"/>
@@ -3230,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J42" t="str">
         <f t="shared" si="0"/>
@@ -3242,7 +3245,7 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -3263,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J43" t="str">
         <f t="shared" si="0"/>
@@ -3296,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J44" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3329,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J45" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3362,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J46" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3395,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J47" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3428,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J48" t="str">
         <f t="shared" si="0"/>
@@ -3461,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J49" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3494,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J50" t="str">
         <f t="shared" si="0"/>
@@ -3527,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J51" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3539,7 +3542,7 @@
         <v>58</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C52" s="2">
         <v>2</v>
@@ -3560,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J52" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3572,7 +3575,7 @@
         <v>59</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C53" s="2">
         <v>3</v>
@@ -3593,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J53" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3605,7 +3608,7 @@
         <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -3626,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J54" t="str">
         <f t="shared" si="0"/>
@@ -3659,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J55" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3692,7 +3695,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J56" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3704,7 +3707,7 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C57">
         <v>3</v>
@@ -3725,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J57" t="str">
         <f t="shared" si="0"/>
@@ -3737,7 +3740,7 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -3758,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J58" t="str">
         <f t="shared" si="0"/>
@@ -3791,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J59" t="str">
         <f t="shared" si="0"/>
@@ -3824,7 +3827,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J60" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3836,7 +3839,7 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -3857,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J61" t="str">
         <f t="shared" ref="J61" si="1">CONCATENATE("walking","_","Tx",A61)</f>
@@ -3869,7 +3872,7 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -3890,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J62" t="str">
         <f t="shared" ref="J62" si="2">CONCATENATE("walking","_","Tx",A62)</f>
@@ -3933,7 +3936,7 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3944,7 +3947,7 @@
         <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3952,10 +3955,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3966,7 +3969,7 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3977,7 +3980,7 @@
         <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3985,10 +3988,10 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3999,7 +4002,7 @@
         <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4010,7 +4013,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4018,10 +4021,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>175</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -4066,13 +4069,13 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -4315,16 +4318,16 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
@@ -4564,19 +4567,19 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F4" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -4813,7 +4816,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C5" t="s">
         <v>117</v>
@@ -5062,16 +5065,16 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C6" t="s">
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
@@ -5311,13 +5314,13 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C7" t="s">
         <v>116</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -5560,16 +5563,16 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C8" t="s">
         <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E8" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
@@ -5809,16 +5812,16 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E9" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F9" t="s">
         <v>19</v>
@@ -6058,10 +6061,10 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D10" t="s">
         <v>63</v>
@@ -6307,13 +6310,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C11" t="s">
         <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -6556,13 +6559,13 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C12" t="s">
         <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E12" t="s">
         <v>20</v>
@@ -6805,7 +6808,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C13" t="s">
         <v>103</v>
@@ -7054,13 +7057,13 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C14" t="s">
         <v>119</v>
       </c>
       <c r="D14" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -7303,13 +7306,13 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -7552,13 +7555,13 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C16" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D16" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
@@ -7801,13 +7804,13 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C17" t="s">
         <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
@@ -8050,13 +8053,13 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C18" t="s">
         <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E18" t="s">
         <v>21</v>
@@ -8299,10 +8302,10 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C19" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D19" t="s">
         <v>60</v>
@@ -8548,13 +8551,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C20" t="s">
         <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E20" t="s">
         <v>23</v>
@@ -8797,13 +8800,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C21" t="s">
         <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E21" t="s">
         <v>20</v>
@@ -9046,7 +9049,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C22" t="s">
         <v>106</v>
@@ -9058,7 +9061,7 @@
         <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G22"/>
       <c r="H22"/>
@@ -9295,10 +9298,10 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C23" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D23" t="s">
         <v>73</v>
@@ -9307,7 +9310,7 @@
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:235">
@@ -9315,16 +9318,16 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C24" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D24" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E24" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -9335,10 +9338,10 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
         <v>73</v>
@@ -9347,7 +9350,7 @@
         <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:235">
@@ -9355,7 +9358,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C26" t="s">
         <v>102</v>
@@ -9367,7 +9370,7 @@
         <v>20</v>
       </c>
       <c r="F26" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:235">
@@ -9375,7 +9378,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C27" t="s">
         <v>106</v>
@@ -9387,7 +9390,7 @@
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:235">
@@ -9395,13 +9398,13 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C28" t="s">
         <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E28" t="s">
         <v>23</v>
@@ -9411,12 +9414,24 @@
       </c>
     </row>
     <row r="29" spans="1:235" s="2" customFormat="1">
-      <c r="A29"/>
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
+      <c r="A29">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>263</v>
+      </c>
+      <c r="C29" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" t="s">
+        <v>256</v>
+      </c>
+      <c r="E29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" t="s">
+        <v>13</v>
+      </c>
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29"/>
@@ -9673,46 +9688,46 @@
     </row>
     <row r="2" spans="1:4" ht="78">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="156">
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="31.2">
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="187.2">
       <c r="B5" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D5" t="s">
         <v>60</v>
@@ -9720,10 +9735,10 @@
     </row>
     <row r="6" spans="1:4" ht="62.4">
       <c r="B6" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="D6" t="s">
         <v>73</v>
@@ -9731,24 +9746,24 @@
     </row>
     <row r="7" spans="1:4" ht="46.8">
       <c r="A7" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="187.2">
       <c r="B8" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
@@ -9759,7 +9774,7 @@
         <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D9" t="s">
         <v>61</v>
@@ -9770,10 +9785,10 @@
         <v>48</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="187.2">
@@ -9781,7 +9796,7 @@
         <v>53</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D11" t="s">
         <v>65</v>
@@ -9789,10 +9804,10 @@
     </row>
     <row r="12" spans="1:4" ht="156">
       <c r="B12" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
         <v>73</v>
@@ -9800,16 +9815,16 @@
     </row>
     <row r="13" spans="1:4" ht="46.8">
       <c r="A13" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="374.4">
@@ -9817,7 +9832,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
@@ -9828,7 +9843,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D15" t="s">
         <v>63</v>
@@ -9836,13 +9851,13 @@
     </row>
     <row r="16" spans="1:4" ht="156">
       <c r="A16" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D16" t="s">
         <v>64</v>
@@ -9850,10 +9865,10 @@
     </row>
     <row r="17" spans="1:4" ht="109.2">
       <c r="B17" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
         <v>71</v>
@@ -9861,10 +9876,10 @@
     </row>
     <row r="18" spans="1:4" ht="156">
       <c r="B18" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D18" t="s">
         <v>73</v>
@@ -9872,13 +9887,13 @@
     </row>
     <row r="19" spans="1:4" ht="234">
       <c r="A19" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D19" t="s">
         <v>61</v>
@@ -9889,7 +9904,7 @@
         <v>53</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D20" t="s">
         <v>65</v>
@@ -9900,7 +9915,7 @@
         <v>54</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D21" t="s">
         <v>66</v>
@@ -9908,13 +9923,13 @@
     </row>
     <row r="22" spans="1:4" ht="187.2">
       <c r="A22" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D22" t="s">
         <v>60</v>
@@ -9925,7 +9940,7 @@
         <v>47</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D23" t="s">
         <v>61</v>
@@ -9936,7 +9951,7 @@
         <v>53</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
         <v>65</v>
@@ -9958,7 +9973,7 @@
         <v>56</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D26" t="s">
         <v>68</v>
@@ -9980,7 +9995,7 @@
         <v>59</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D28" t="s">
         <v>60</v>
@@ -9988,10 +10003,10 @@
     </row>
     <row r="29" spans="1:4" ht="62.4">
       <c r="B29" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="D29" t="s">
         <v>73</v>
@@ -9999,13 +10014,13 @@
     </row>
     <row r="30" spans="1:4" ht="265.2">
       <c r="A30" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
         <v>73</v>
@@ -10016,7 +10031,7 @@
         <v>57</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
         <v>70</v>
@@ -10024,10 +10039,10 @@
     </row>
     <row r="32" spans="1:4" ht="93.6">
       <c r="B32" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D32" t="s">
         <v>72</v>
@@ -10038,7 +10053,7 @@
         <v>53</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D33" t="s">
         <v>65</v>
@@ -10057,7 +10072,7 @@
     </row>
     <row r="35" spans="1:4" ht="62.4">
       <c r="A35" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>58</v>
@@ -10074,7 +10089,7 @@
         <v>57</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D36" t="s">
         <v>70</v>
@@ -10082,16 +10097,16 @@
     </row>
     <row r="37" spans="1:4" ht="62.4">
       <c r="A37" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="234">
@@ -10099,7 +10114,7 @@
         <v>47</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D38" t="s">
         <v>61</v>
@@ -10110,7 +10125,7 @@
         <v>49</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D39" t="s">
         <v>62</v>
@@ -10121,7 +10136,7 @@
         <v>53</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D40" t="s">
         <v>65</v>
@@ -10140,10 +10155,10 @@
     </row>
     <row r="42" spans="1:4" ht="62.4">
       <c r="B42" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="D42" t="s">
         <v>73</v>
@@ -10186,7 +10201,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -10261,7 +10276,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
+++ b/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wanho\Documents\kate_gait_subjective\gaitanalysersubjective\app\jsonfiles\excel\stance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A78BC11-5C6C-4B5F-886E-D09397AC9D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C2AFE9-D9D0-4FB8-ACFB-66F3228D06D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9410,7 +9410,7 @@
         <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:235" s="2" customFormat="1">

--- a/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
+++ b/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wanho\Documents\kate_gait_subjective\gaitanalysersubjective\app\jsonfiles\excel\stance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C2AFE9-D9D0-4FB8-ACFB-66F3228D06D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C508CC62-638D-459F-9068-FA80291185D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="treatments" sheetId="1" r:id="rId1"/>
@@ -4039,7 +4039,7 @@
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.6"/>
   <cols>
     <col min="2" max="2" width="60.8984375" customWidth="1"/>
-    <col min="3" max="3" width="5.69921875" customWidth="1"/>
+    <col min="3" max="3" width="16.09765625" customWidth="1"/>
     <col min="4" max="4" width="54.69921875" customWidth="1"/>
     <col min="5" max="5" width="57.796875" customWidth="1"/>
   </cols>

--- a/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
+++ b/app/jsonfiles/excel/stance/stance_walking_tool_15_04_2024_excel.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wanho\Documents\kate_gait_subjective\gaitanalysersubjective\app\jsonfiles\excel\stance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C508CC62-638D-459F-9068-FA80291185D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC93B16-CCAB-414B-BAB8-248ACC6E2812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="treatments" sheetId="1" r:id="rId1"/>
-    <sheet name="kinematic_deviations" sheetId="2" r:id="rId2"/>
-    <sheet name="impairments" sheetId="3" r:id="rId3"/>
+    <sheet name="kinematic_deviations" sheetId="2" r:id="rId1"/>
+    <sheet name="impairments" sheetId="3" r:id="rId2"/>
+    <sheet name="treatments" sheetId="1" r:id="rId3"/>
     <sheet name="table" sheetId="5" r:id="rId4"/>
     <sheet name="Keys" sheetId="4" r:id="rId5"/>
   </sheets>
@@ -1846,2069 +1846,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J62"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.6"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="79.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>231</v>
-      </c>
-      <c r="J1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="2" customFormat="1">
-      <c r="A2" s="2">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J2" s="2" t="str">
-        <f>CONCATENATE("walking","_","Tx",A2)</f>
-        <v>walking_Tx2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="2" customFormat="1">
-      <c r="A3" s="2">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="2">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J3" s="2" t="str">
-        <f t="shared" ref="J3:J60" si="0">CONCATENATE("walking","_","Tx",A3)</f>
-        <v>walking_Tx3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="2" customFormat="1">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="2">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J4" s="2" t="str">
-        <f>CONCATENATE("walking","_","Tx",A4)</f>
-        <v>walking_Tx4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="2" customFormat="1">
-      <c r="A5" s="2">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="2">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J5" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="2" customFormat="1">
-      <c r="A6" s="2">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J6" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="2" customFormat="1">
-      <c r="A7" s="2">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C7" s="2">
-        <v>3</v>
-      </c>
-      <c r="D7" s="2">
-        <v>2</v>
-      </c>
-      <c r="E7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J7" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" ht="31.2">
-      <c r="A8" s="2">
-        <v>8</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="2">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J8" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="2" customFormat="1">
-      <c r="A9" s="2">
-        <v>9</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="2">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J9" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="2" customFormat="1">
-      <c r="A10" s="2">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="2">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J10" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="2" customFormat="1">
-      <c r="A11" s="2">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="2">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J11" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J12" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>219</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J13" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="2" customFormat="1">
-      <c r="A14" s="2">
-        <v>14</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J14" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="2" customFormat="1">
-      <c r="A15" s="2">
-        <v>15</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C15" s="2">
-        <v>3</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="E15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J15" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="2" customFormat="1">
-      <c r="A16" s="2">
-        <v>16</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C16" s="2">
-        <v>3</v>
-      </c>
-      <c r="D16" s="2">
-        <v>1</v>
-      </c>
-      <c r="E16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J16" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="2" customFormat="1">
-      <c r="A17" s="2">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="2">
-        <v>3</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J17" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="2" customFormat="1">
-      <c r="A18" s="2">
-        <v>18</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="2">
-        <v>3</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
-      <c r="E18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J18" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" s="2" customFormat="1">
-      <c r="A19" s="2">
-        <v>19</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="2">
-        <v>3</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J19" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="2" customFormat="1">
-      <c r="A20" s="2">
-        <v>20</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C20" s="2">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J20" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" s="2" customFormat="1">
-      <c r="A21" s="2">
-        <v>21</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J21" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" s="2" customFormat="1">
-      <c r="A22" s="2">
-        <v>22</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
-      <c r="E22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J22" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="2" customFormat="1">
-      <c r="A23" s="2">
-        <v>23</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="2">
-        <v>2</v>
-      </c>
-      <c r="D23" s="2">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J23" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" s="2" customFormat="1">
-      <c r="A24" s="2">
-        <v>24</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C24" s="2">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J24" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" s="2" customFormat="1">
-      <c r="A25" s="2">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" s="2">
-        <v>2</v>
-      </c>
-      <c r="D25" s="2">
-        <v>1</v>
-      </c>
-      <c r="E25" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J25" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" s="2" customFormat="1">
-      <c r="A26" s="2">
-        <v>26</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C26" s="2">
-        <v>2</v>
-      </c>
-      <c r="D26" s="2">
-        <v>1</v>
-      </c>
-      <c r="E26" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G26" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J26" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" s="2" customFormat="1">
-      <c r="A27" s="2">
-        <v>27</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C27" s="2">
-        <v>2</v>
-      </c>
-      <c r="D27" s="2">
-        <v>1</v>
-      </c>
-      <c r="E27" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J27" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" s="2" customFormat="1">
-      <c r="A28" s="2">
-        <v>28</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="2">
-        <v>3</v>
-      </c>
-      <c r="D28" s="2">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J28" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" s="2" customFormat="1">
-      <c r="A29" s="2">
-        <v>29</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="2">
-        <v>2</v>
-      </c>
-      <c r="D29" s="2">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J29" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" s="2" customFormat="1">
-      <c r="A30" s="2">
-        <v>30</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" s="2">
-        <v>2</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J30" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="2" customFormat="1">
-      <c r="A31" s="2">
-        <v>31</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" s="2">
-        <v>2</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J31" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" s="2" customFormat="1">
-      <c r="A32" s="2">
-        <v>32</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="2">
-        <v>3</v>
-      </c>
-      <c r="D32" s="2">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J32" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33">
-        <v>33</v>
-      </c>
-      <c r="B33" t="s">
-        <v>222</v>
-      </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" t="b">
-        <v>1</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="J33" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34">
-        <v>34</v>
-      </c>
-      <c r="B34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J34" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" s="2" customFormat="1">
-      <c r="A35" s="2">
-        <v>35</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C35" s="2">
-        <v>1</v>
-      </c>
-      <c r="D35" s="2">
-        <v>1</v>
-      </c>
-      <c r="E35" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J35" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36">
-        <v>36</v>
-      </c>
-      <c r="B36" t="s">
-        <v>162</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J36" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37">
-        <v>37</v>
-      </c>
-      <c r="B37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J37" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38">
-        <v>38</v>
-      </c>
-      <c r="B38" t="s">
-        <v>224</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" t="b">
-        <v>1</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="J38" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39">
-        <v>39</v>
-      </c>
-      <c r="B39" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J39" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" s="2" customFormat="1">
-      <c r="A40" s="2">
-        <v>40</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" s="2">
-        <v>1</v>
-      </c>
-      <c r="D40" s="2">
-        <v>1</v>
-      </c>
-      <c r="E40" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J40" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41">
-        <v>41</v>
-      </c>
-      <c r="B41" t="s">
-        <v>95</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" t="b">
-        <v>1</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="J41" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42">
-        <v>42</v>
-      </c>
-      <c r="B42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" t="b">
-        <v>0</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="J42" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43">
-        <v>43</v>
-      </c>
-      <c r="B43" t="s">
-        <v>163</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J43" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" s="2" customFormat="1">
-      <c r="A44" s="2">
-        <v>45</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C44" s="2">
-        <v>1</v>
-      </c>
-      <c r="D44" s="2">
-        <v>1</v>
-      </c>
-      <c r="E44" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J44" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" s="2" customFormat="1">
-      <c r="A45" s="2">
-        <v>46</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C45" s="2">
-        <v>1</v>
-      </c>
-      <c r="D45" s="2">
-        <v>1</v>
-      </c>
-      <c r="E45" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H45" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J45" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" s="2" customFormat="1">
-      <c r="A46" s="2">
-        <v>47</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C46" s="2">
-        <v>1</v>
-      </c>
-      <c r="D46" s="2">
-        <v>1</v>
-      </c>
-      <c r="E46" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J46" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" s="2" customFormat="1">
-      <c r="A47" s="2">
-        <v>48</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C47" s="2">
-        <v>2</v>
-      </c>
-      <c r="D47" s="2">
-        <v>2</v>
-      </c>
-      <c r="E47" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J47" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48">
-        <v>49</v>
-      </c>
-      <c r="B48" t="s">
-        <v>104</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48">
-        <v>2</v>
-      </c>
-      <c r="E48" t="b">
-        <v>0</v>
-      </c>
-      <c r="F48" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J48" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" s="2" customFormat="1">
-      <c r="A49" s="2">
-        <v>51</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C49" s="2">
-        <v>1</v>
-      </c>
-      <c r="D49" s="2">
-        <v>2</v>
-      </c>
-      <c r="E49" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J49" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx51</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50">
-        <v>56</v>
-      </c>
-      <c r="B50" t="s">
-        <v>108</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J50" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx56</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" s="2" customFormat="1">
-      <c r="A51" s="2">
-        <v>57</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51" s="2">
-        <v>2</v>
-      </c>
-      <c r="D51" s="2">
-        <v>1</v>
-      </c>
-      <c r="E51" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H51" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J51" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx57</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" s="2" customFormat="1">
-      <c r="A52" s="2">
-        <v>58</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C52" s="2">
-        <v>2</v>
-      </c>
-      <c r="D52" s="2">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H52" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J52" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx58</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" s="2" customFormat="1">
-      <c r="A53" s="2">
-        <v>59</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C53" s="2">
-        <v>3</v>
-      </c>
-      <c r="D53" s="2">
-        <v>1</v>
-      </c>
-      <c r="E53" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H53" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J53" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx59</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54">
-        <v>60</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-      <c r="E54" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" t="b">
-        <v>1</v>
-      </c>
-      <c r="G54" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" t="b">
-        <v>0</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="J54" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" s="2" customFormat="1">
-      <c r="A55" s="2">
-        <v>61</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C55" s="2">
-        <v>3</v>
-      </c>
-      <c r="D55" s="2">
-        <v>1</v>
-      </c>
-      <c r="E55" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G55" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J55" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" s="2" customFormat="1">
-      <c r="A56" s="2">
-        <v>62</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C56" s="2">
-        <v>2</v>
-      </c>
-      <c r="D56" s="2">
-        <v>1</v>
-      </c>
-      <c r="E56" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J56" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx62</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57">
-        <v>63</v>
-      </c>
-      <c r="B57" t="s">
-        <v>170</v>
-      </c>
-      <c r="C57">
-        <v>3</v>
-      </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J57" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58">
-        <v>64</v>
-      </c>
-      <c r="B58" t="s">
-        <v>226</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58" t="b">
-        <v>0</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="J58" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59">
-        <v>65</v>
-      </c>
-      <c r="B59" t="s">
-        <v>108</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59" t="b">
-        <v>0</v>
-      </c>
-      <c r="F59" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J59" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" s="2" customFormat="1">
-      <c r="A60" s="2">
-        <v>66</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C60" s="2">
-        <v>2</v>
-      </c>
-      <c r="D60" s="2">
-        <v>1</v>
-      </c>
-      <c r="E60" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F60" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G60" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J60" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>walking_Tx66</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61">
-        <v>67</v>
-      </c>
-      <c r="B61" t="s">
-        <v>245</v>
-      </c>
-      <c r="C61">
-        <v>2</v>
-      </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" t="b">
-        <v>1</v>
-      </c>
-      <c r="G61" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" t="b">
-        <v>0</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J61" t="str">
-        <f t="shared" ref="J61" si="1">CONCATENATE("walking","_","Tx",A61)</f>
-        <v>walking_Tx67</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62">
-        <v>68</v>
-      </c>
-      <c r="B62" t="s">
-        <v>246</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="E62" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" t="b">
-        <v>1</v>
-      </c>
-      <c r="G62" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" t="b">
-        <v>0</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J62" t="str">
-        <f t="shared" ref="J62" si="2">CONCATENATE("walking","_","Tx",A62)</f>
-        <v>walking_Tx68</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="B1 D8:H8 C12:H13 D9:H11 E22:H22 D18:H20 C26 D24:H24 C33:H39 D28:H32 C1:H1 C41:H42 C5:H5 C2 E2:H2 E3:H3 D4:H4 D6:H6 D7:H7 D16:H16 D40:H40 C15 C14 E14:H14 E15:H15 E17:H17 E21:H21 E23:H23 E25:H25 E26:H26 E27:H27" numberStoredAsText="1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C10"/>
@@ -4032,7 +1969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:IA29"/>
@@ -9670,6 +7607,2069 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:J62"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="79.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J2" s="2" t="str">
+        <f>CONCATENATE("walking","_","Tx",A2)</f>
+        <v>walking_Tx2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="2" customFormat="1">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J3" s="2" t="str">
+        <f t="shared" ref="J3:J60" si="0">CONCATENATE("walking","_","Tx",A3)</f>
+        <v>walking_Tx3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="2" customFormat="1">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J4" s="2" t="str">
+        <f>CONCATENATE("walking","_","Tx",A4)</f>
+        <v>walking_Tx4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="2" customFormat="1">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="2" customFormat="1">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="2" customFormat="1">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="2" customFormat="1" ht="31.2">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="2" customFormat="1">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="2" customFormat="1">
+      <c r="A10" s="2">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="2" customFormat="1">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="2" customFormat="1">
+      <c r="A14" s="2">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="2" customFormat="1">
+      <c r="A15" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="2" customFormat="1">
+      <c r="A16" s="2">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="2" customFormat="1">
+      <c r="A17" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="2" customFormat="1">
+      <c r="A18" s="2">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="2">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J18" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="2" customFormat="1">
+      <c r="A19" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="2">
+        <v>3</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J19" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="2" customFormat="1">
+      <c r="A20" s="2">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J20" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="2" customFormat="1">
+      <c r="A21" s="2">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J21" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="2" customFormat="1">
+      <c r="A22" s="2">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J22" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="2" customFormat="1">
+      <c r="A23" s="2">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="2" customFormat="1">
+      <c r="A24" s="2">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J24" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="2" customFormat="1">
+      <c r="A25" s="2">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J25" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="2" customFormat="1">
+      <c r="A26" s="2">
+        <v>26</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J26" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" s="2" customFormat="1">
+      <c r="A27" s="2">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J27" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="2" customFormat="1">
+      <c r="A28" s="2">
+        <v>28</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="2">
+        <v>3</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J28" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" s="2" customFormat="1">
+      <c r="A29" s="2">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="2">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J29" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="2" customFormat="1">
+      <c r="A30" s="2">
+        <v>30</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="2">
+        <v>2</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J30" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" s="2" customFormat="1">
+      <c r="A31" s="2">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J31" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" s="2" customFormat="1">
+      <c r="A32" s="2">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="2">
+        <v>3</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J32" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>222</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="2" customFormat="1">
+      <c r="A35" s="2">
+        <v>35</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1</v>
+      </c>
+      <c r="E35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J35" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>224</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J38" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" s="2" customFormat="1">
+      <c r="A40" s="2">
+        <v>40</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1</v>
+      </c>
+      <c r="E40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J40" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" s="2" customFormat="1">
+      <c r="A44" s="2">
+        <v>45</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>1</v>
+      </c>
+      <c r="E44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J44" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" s="2" customFormat="1">
+      <c r="A45" s="2">
+        <v>46</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2">
+        <v>1</v>
+      </c>
+      <c r="E45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J45" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" s="2" customFormat="1">
+      <c r="A46" s="2">
+        <v>47</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>1</v>
+      </c>
+      <c r="E46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J46" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" s="2" customFormat="1">
+      <c r="A47" s="2">
+        <v>48</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="2">
+        <v>2</v>
+      </c>
+      <c r="D47" s="2">
+        <v>2</v>
+      </c>
+      <c r="E47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J47" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J48" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" s="2" customFormat="1">
+      <c r="A49" s="2">
+        <v>51</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2</v>
+      </c>
+      <c r="E49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J49" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50">
+        <v>56</v>
+      </c>
+      <c r="B50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J50" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" s="2" customFormat="1">
+      <c r="A51" s="2">
+        <v>57</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="2">
+        <v>2</v>
+      </c>
+      <c r="D51" s="2">
+        <v>1</v>
+      </c>
+      <c r="E51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J51" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" s="2" customFormat="1">
+      <c r="A52" s="2">
+        <v>58</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C52" s="2">
+        <v>2</v>
+      </c>
+      <c r="D52" s="2">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J52" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" s="2" customFormat="1">
+      <c r="A53" s="2">
+        <v>59</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C53" s="2">
+        <v>3</v>
+      </c>
+      <c r="D53" s="2">
+        <v>1</v>
+      </c>
+      <c r="E53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J53" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54">
+        <v>60</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" s="2" customFormat="1">
+      <c r="A55" s="2">
+        <v>61</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="2">
+        <v>3</v>
+      </c>
+      <c r="D55" s="2">
+        <v>1</v>
+      </c>
+      <c r="E55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J55" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" s="2" customFormat="1">
+      <c r="A56" s="2">
+        <v>62</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" s="2">
+        <v>2</v>
+      </c>
+      <c r="D56" s="2">
+        <v>1</v>
+      </c>
+      <c r="E56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J56" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57">
+        <v>63</v>
+      </c>
+      <c r="B57" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J57" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58">
+        <v>64</v>
+      </c>
+      <c r="B58" t="s">
+        <v>226</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58" t="b">
+        <v>0</v>
+      </c>
+      <c r="F58" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J58" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59">
+        <v>65</v>
+      </c>
+      <c r="B59" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59" t="b">
+        <v>0</v>
+      </c>
+      <c r="F59" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" s="2" customFormat="1">
+      <c r="A60" s="2">
+        <v>66</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" s="2">
+        <v>2</v>
+      </c>
+      <c r="D60" s="2">
+        <v>1</v>
+      </c>
+      <c r="E60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J60" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>walking_Tx66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61">
+        <v>67</v>
+      </c>
+      <c r="B61" t="s">
+        <v>245</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" t="b">
+        <v>1</v>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" ref="J61" si="1">CONCATENATE("walking","_","Tx",A61)</f>
+        <v>walking_Tx67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62">
+        <v>68</v>
+      </c>
+      <c r="B62" t="s">
+        <v>246</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" t="b">
+        <v>1</v>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J62" t="str">
+        <f t="shared" ref="J62" si="2">CONCATENATE("walking","_","Tx",A62)</f>
+        <v>walking_Tx68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="B1 D8:H8 C12:H13 D9:H11 E22:H22 D18:H20 C26 D24:H24 C33:H39 D28:H32 C1:H1 C41:H42 C5:H5 C2 E2:H2 E3:H3 D4:H4 D6:H6 D7:H7 D16:H16 D40:H40 C15 C14 E14:H14 E15:H15 E17:H17 E21:H21 E23:H23 E25:H25 E26:H26 E27:H27" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB19E346-4EBF-493E-9E0F-B96C0963746A}">
   <sheetPr codeName="Sheet4"/>
